--- a/Data/#U0e23#U0e32#U0e22#U0e07#U0e32#U0e19#U0e1b#U0e23#U0e30#U0e08#U0e33#U0e27#U0e31#U0e19#U0e0a#U0e38#U0e21#U0e2a#U0e32#U0e22 v2.5.xlsx
+++ b/Data/#U0e23#U0e32#U0e22#U0e07#U0e32#U0e19#U0e1b#U0e23#U0e30#U0e08#U0e33#U0e27#U0e31#U0e19#U0e0a#U0e38#U0e21#U0e2a#U0e32#U0e22 v2.5.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Forth\0.USO\Anitigravity\Gang3Cha\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67F4C501-BD5A-486B-B531-904C91BDCCEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5036545-E0CC-4734-916D-578D7D61B5B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="202" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1083" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1543" uniqueCount="339">
   <si>
     <t>การจัดซื้ออุปกรณ์พร้อมดำเนินการติดตั้ง
 โครงการเพิ่มประสิทธิภาพระบบโครงข่ายสื่อสารด้วยอุปกรณ์ทวนสัญญาณผ่านคลื่นความถี่สูง (SHF)
@@ -1653,7 +1653,7 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1828,6 +1828,27 @@
         </ext>
       </extLst>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="8" borderId="0" xfId="15" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1835,15 +1856,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1864,18 +1876,6 @@
     <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1887,6 +1887,9 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="16">
@@ -4592,10 +4595,10 @@
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>8</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8856,64 +8859,64 @@
     <row r="1" spans="2:24" ht="71.400000000000006" customHeight="1">
       <c r="B1" s="30"/>
       <c r="C1" s="31"/>
-      <c r="D1" s="63" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" s="63"/>
-      <c r="F1" s="63"/>
-      <c r="G1" s="63"/>
-      <c r="H1" s="63"/>
-      <c r="I1" s="63"/>
-      <c r="J1" s="63"/>
-      <c r="K1" s="63"/>
-      <c r="L1" s="63"/>
-      <c r="M1" s="63"/>
-      <c r="N1" s="63"/>
-      <c r="O1" s="63"/>
+      <c r="D1" s="70" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
+      <c r="I1" s="70"/>
+      <c r="J1" s="70"/>
+      <c r="K1" s="70"/>
+      <c r="L1" s="70"/>
+      <c r="M1" s="70"/>
+      <c r="N1" s="70"/>
+      <c r="O1" s="70"/>
       <c r="P1" s="32"/>
       <c r="Q1" s="32"/>
-      <c r="U1" s="62"/>
-      <c r="V1" s="62"/>
-      <c r="W1" s="62"/>
+      <c r="U1" s="69"/>
+      <c r="V1" s="69"/>
+      <c r="W1" s="69"/>
       <c r="X1" s="30"/>
     </row>
     <row r="2" spans="2:24" ht="25.2" customHeight="1">
-      <c r="B2" s="64"/>
-      <c r="C2" s="64"/>
-      <c r="D2" s="64"/>
-      <c r="E2" s="64"/>
-      <c r="F2" s="64"/>
-      <c r="G2" s="64"/>
-      <c r="H2" s="64"/>
-      <c r="I2" s="64"/>
-      <c r="J2" s="64"/>
-      <c r="K2" s="64"/>
-      <c r="L2" s="64"/>
-      <c r="M2" s="64"/>
-      <c r="N2" s="64"/>
-      <c r="O2" s="64"/>
-      <c r="P2" s="64"/>
-      <c r="Q2" s="64"/>
+      <c r="B2" s="71"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="71"/>
+      <c r="G2" s="71"/>
+      <c r="H2" s="71"/>
+      <c r="I2" s="71"/>
+      <c r="J2" s="71"/>
+      <c r="K2" s="71"/>
+      <c r="L2" s="71"/>
+      <c r="M2" s="71"/>
+      <c r="N2" s="71"/>
+      <c r="O2" s="71"/>
+      <c r="P2" s="71"/>
+      <c r="Q2" s="71"/>
     </row>
     <row r="3" spans="2:24" ht="31.95" customHeight="1">
-      <c r="B3" s="68" t="s">
+      <c r="B3" s="72" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="68"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="68"/>
-      <c r="H3" s="68"/>
-      <c r="I3" s="68"/>
-      <c r="J3" s="68"/>
-      <c r="K3" s="68"/>
-      <c r="L3" s="68"/>
-      <c r="M3" s="68"/>
-      <c r="N3" s="68"/>
-      <c r="O3" s="68"/>
-      <c r="P3" s="68"/>
-      <c r="Q3" s="68"/>
+      <c r="C3" s="72"/>
+      <c r="D3" s="72"/>
+      <c r="E3" s="72"/>
+      <c r="F3" s="72"/>
+      <c r="G3" s="72"/>
+      <c r="H3" s="72"/>
+      <c r="I3" s="72"/>
+      <c r="J3" s="72"/>
+      <c r="K3" s="72"/>
+      <c r="L3" s="72"/>
+      <c r="M3" s="72"/>
+      <c r="N3" s="72"/>
+      <c r="O3" s="72"/>
+      <c r="P3" s="72"/>
+      <c r="Q3" s="72"/>
     </row>
     <row r="4" spans="2:24" ht="21">
       <c r="B4" s="28" t="s">
@@ -8921,7 +8924,7 @@
       </c>
       <c r="C4" s="29">
         <f ca="1">TODAY()</f>
-        <v>46288</v>
+        <v>46301</v>
       </c>
       <c r="D4" s="21"/>
       <c r="E4" s="7"/>
@@ -8939,80 +8942,80 @@
       <c r="Q4" s="7"/>
     </row>
     <row r="5" spans="2:24" ht="21">
-      <c r="B5" s="73" t="s">
+      <c r="B5" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="73"/>
-      <c r="D5" s="73"/>
-      <c r="E5" s="73"/>
-      <c r="F5" s="73"/>
-      <c r="G5" s="73"/>
-      <c r="H5" s="73"/>
-      <c r="I5" s="73"/>
-      <c r="J5" s="73"/>
-      <c r="K5" s="73"/>
-      <c r="L5" s="73"/>
-      <c r="M5" s="73"/>
-      <c r="N5" s="73"/>
-      <c r="O5" s="73"/>
-      <c r="P5" s="73"/>
-      <c r="Q5" s="73"/>
+      <c r="C5" s="77"/>
+      <c r="D5" s="77"/>
+      <c r="E5" s="77"/>
+      <c r="F5" s="77"/>
+      <c r="G5" s="77"/>
+      <c r="H5" s="77"/>
+      <c r="I5" s="77"/>
+      <c r="J5" s="77"/>
+      <c r="K5" s="77"/>
+      <c r="L5" s="77"/>
+      <c r="M5" s="77"/>
+      <c r="N5" s="77"/>
+      <c r="O5" s="77"/>
+      <c r="P5" s="77"/>
+      <c r="Q5" s="77"/>
     </row>
     <row r="6" spans="2:24" ht="39.6" customHeight="1">
-      <c r="B6" s="70" t="s">
+      <c r="B6" s="74" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="70"/>
-      <c r="D6" s="70"/>
-      <c r="E6" s="70"/>
-      <c r="F6" s="69" t="s">
+      <c r="C6" s="74"/>
+      <c r="D6" s="74"/>
+      <c r="E6" s="74"/>
+      <c r="F6" s="73" t="s">
         <v>5</v>
       </c>
-      <c r="G6" s="69"/>
-      <c r="H6" s="69"/>
-      <c r="I6" s="69"/>
-      <c r="J6" s="69" t="s">
+      <c r="G6" s="73"/>
+      <c r="H6" s="73"/>
+      <c r="I6" s="73"/>
+      <c r="J6" s="73" t="s">
         <v>6</v>
       </c>
-      <c r="K6" s="69"/>
-      <c r="L6" s="69"/>
-      <c r="M6" s="69"/>
-      <c r="N6" s="72" t="s">
+      <c r="K6" s="73"/>
+      <c r="L6" s="73"/>
+      <c r="M6" s="73"/>
+      <c r="N6" s="76" t="s">
         <v>7</v>
       </c>
-      <c r="O6" s="72"/>
-      <c r="P6" s="72"/>
-      <c r="Q6" s="72"/>
+      <c r="O6" s="76"/>
+      <c r="P6" s="76"/>
+      <c r="Q6" s="76"/>
     </row>
     <row r="7" spans="2:24" ht="16.95" customHeight="1">
-      <c r="B7" s="71" t="str">
+      <c r="B7" s="75" t="str">
         <f>" สถานะ : "&amp;Overview!$W$3</f>
         <v xml:space="preserve"> สถานะ : ปกติ / Normal</v>
       </c>
-      <c r="C7" s="71"/>
-      <c r="D7" s="71"/>
-      <c r="E7" s="71"/>
-      <c r="F7" s="71" t="str">
+      <c r="C7" s="75"/>
+      <c r="D7" s="75"/>
+      <c r="E7" s="75"/>
+      <c r="F7" s="75" t="str">
         <f>" สถานะ : "&amp;Overview!$W$4</f>
         <v xml:space="preserve"> สถานะ : ปกติ / Normal</v>
       </c>
-      <c r="G7" s="71"/>
-      <c r="H7" s="71"/>
-      <c r="I7" s="71"/>
-      <c r="J7" s="71" t="str">
+      <c r="G7" s="75"/>
+      <c r="H7" s="75"/>
+      <c r="I7" s="75"/>
+      <c r="J7" s="75" t="str">
         <f>" สถานะ : "&amp;Overview!$W$5</f>
         <v xml:space="preserve"> สถานะ : ปกติ / Normal</v>
       </c>
-      <c r="K7" s="71"/>
-      <c r="L7" s="71"/>
-      <c r="M7" s="71"/>
-      <c r="N7" s="71" t="str">
+      <c r="K7" s="75"/>
+      <c r="L7" s="75"/>
+      <c r="M7" s="75"/>
+      <c r="N7" s="75" t="str">
         <f>" สถานะ : "&amp;Overview!$W$6</f>
         <v xml:space="preserve"> สถานะ : ปกติ / Normal</v>
       </c>
-      <c r="O7" s="71"/>
-      <c r="P7" s="71"/>
-      <c r="Q7" s="71"/>
+      <c r="O7" s="75"/>
+      <c r="P7" s="75"/>
+      <c r="Q7" s="75"/>
     </row>
     <row r="8" spans="2:24" ht="21">
       <c r="B8" s="23"/>
@@ -9033,125 +9036,125 @@
       <c r="Q8" s="23"/>
     </row>
     <row r="9" spans="2:24" ht="27" customHeight="1">
-      <c r="B9" s="74" t="s">
+      <c r="B9" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="74"/>
-      <c r="D9" s="74"/>
-      <c r="E9" s="74"/>
-      <c r="F9" s="74"/>
-      <c r="G9" s="74"/>
-      <c r="H9" s="74"/>
-      <c r="I9" s="74"/>
-      <c r="J9" s="74"/>
-      <c r="K9" s="74"/>
-      <c r="L9" s="74"/>
-      <c r="M9" s="74"/>
-      <c r="N9" s="74"/>
-      <c r="O9" s="74"/>
-      <c r="P9" s="74"/>
-      <c r="Q9" s="74"/>
+      <c r="C9" s="65"/>
+      <c r="D9" s="65"/>
+      <c r="E9" s="65"/>
+      <c r="F9" s="65"/>
+      <c r="G9" s="65"/>
+      <c r="H9" s="65"/>
+      <c r="I9" s="65"/>
+      <c r="J9" s="65"/>
+      <c r="K9" s="65"/>
+      <c r="L9" s="65"/>
+      <c r="M9" s="65"/>
+      <c r="N9" s="65"/>
+      <c r="O9" s="65"/>
+      <c r="P9" s="65"/>
+      <c r="Q9" s="65"/>
     </row>
     <row r="10" spans="2:24" ht="27" customHeight="1">
-      <c r="B10" s="75" t="s">
+      <c r="B10" s="66" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="75"/>
-      <c r="D10" s="75"/>
-      <c r="E10" s="75"/>
-      <c r="F10" s="76" t="s">
+      <c r="C10" s="66"/>
+      <c r="D10" s="66"/>
+      <c r="E10" s="66"/>
+      <c r="F10" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="G10" s="77"/>
-      <c r="H10" s="77"/>
-      <c r="I10" s="77"/>
-      <c r="J10" s="75" t="s">
+      <c r="G10" s="68"/>
+      <c r="H10" s="68"/>
+      <c r="I10" s="68"/>
+      <c r="J10" s="66" t="s">
         <v>11</v>
       </c>
-      <c r="K10" s="75"/>
-      <c r="L10" s="75"/>
-      <c r="M10" s="75"/>
-      <c r="N10" s="75"/>
-      <c r="O10" s="75"/>
-      <c r="P10" s="75"/>
-      <c r="Q10" s="75"/>
+      <c r="K10" s="66"/>
+      <c r="L10" s="66"/>
+      <c r="M10" s="66"/>
+      <c r="N10" s="66"/>
+      <c r="O10" s="66"/>
+      <c r="P10" s="66"/>
+      <c r="Q10" s="66"/>
     </row>
     <row r="11" spans="2:24" ht="25.2" customHeight="1">
-      <c r="B11" s="65" t="s">
+      <c r="B11" s="62" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="65"/>
-      <c r="D11" s="65"/>
-      <c r="E11" s="65"/>
-      <c r="F11" s="66" t="str">
+      <c r="C11" s="62"/>
+      <c r="D11" s="62"/>
+      <c r="E11" s="62"/>
+      <c r="F11" s="63" t="str">
         <f>IF(COUNTIF(Overview!$W$3:$W$6,"ขัดข้อง / Down")=0,"ปกติ / Normal","มีเหตุขัดข้อง / Down")</f>
         <v>ปกติ / Normal</v>
       </c>
-      <c r="G11" s="67"/>
-      <c r="H11" s="67"/>
-      <c r="I11" s="67"/>
-      <c r="J11" s="65" t="str">
+      <c r="G11" s="64"/>
+      <c r="H11" s="64"/>
+      <c r="I11" s="64"/>
+      <c r="J11" s="62" t="str">
         <f>IF(COUNTIF(Overview!$W$3:$W$5,"Down / ขัดข้อง")=0,"ระบบให้บริการตามปกติ / All systems operate normally","Action required: see system status sheet / มีระบบที่ต้องเร่งตรวจสอบ โปรดดูชีตข้อมูลสถานะระบบ")</f>
         <v>ระบบให้บริการตามปกติ / All systems operate normally</v>
       </c>
-      <c r="K11" s="65"/>
-      <c r="L11" s="65"/>
-      <c r="M11" s="65"/>
-      <c r="N11" s="65"/>
-      <c r="O11" s="65"/>
-      <c r="P11" s="65"/>
-      <c r="Q11" s="65"/>
+      <c r="K11" s="62"/>
+      <c r="L11" s="62"/>
+      <c r="M11" s="62"/>
+      <c r="N11" s="62"/>
+      <c r="O11" s="62"/>
+      <c r="P11" s="62"/>
+      <c r="Q11" s="62"/>
     </row>
     <row r="12" spans="2:24" ht="25.2" customHeight="1">
-      <c r="B12" s="65" t="s">
+      <c r="B12" s="62" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="65"/>
-      <c r="D12" s="65"/>
-      <c r="E12" s="65"/>
-      <c r="F12" s="66" t="str">
+      <c r="C12" s="62"/>
+      <c r="D12" s="62"/>
+      <c r="E12" s="62"/>
+      <c r="F12" s="63" t="str">
         <f>COUNTA(Overview!$A$5:$A$20)&amp;" จุด  "</f>
         <v xml:space="preserve">16 จุด  </v>
       </c>
-      <c r="G12" s="67"/>
-      <c r="H12" s="67"/>
-      <c r="I12" s="67"/>
-      <c r="J12" s="65" t="s">
+      <c r="G12" s="64"/>
+      <c r="H12" s="64"/>
+      <c r="I12" s="64"/>
+      <c r="J12" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="K12" s="65"/>
-      <c r="L12" s="65"/>
-      <c r="M12" s="65"/>
-      <c r="N12" s="65"/>
-      <c r="O12" s="65"/>
-      <c r="P12" s="65"/>
-      <c r="Q12" s="65"/>
+      <c r="K12" s="62"/>
+      <c r="L12" s="62"/>
+      <c r="M12" s="62"/>
+      <c r="N12" s="62"/>
+      <c r="O12" s="62"/>
+      <c r="P12" s="62"/>
+      <c r="Q12" s="62"/>
     </row>
     <row r="13" spans="2:24" ht="25.2" customHeight="1">
-      <c r="B13" s="65" t="s">
+      <c r="B13" s="62" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="65"/>
-      <c r="D13" s="65"/>
-      <c r="E13" s="65"/>
-      <c r="F13" s="66" t="str">
+      <c r="C13" s="62"/>
+      <c r="D13" s="62"/>
+      <c r="E13" s="62"/>
+      <c r="F13" s="63" t="str">
         <f>Overview!$Q21&amp;" รายการ / items"</f>
-        <v>0 รายการ / items</v>
-      </c>
-      <c r="G13" s="67"/>
-      <c r="H13" s="67"/>
-      <c r="I13" s="67"/>
-      <c r="J13" s="65" t="str">
+        <v>1 รายการ / items</v>
+      </c>
+      <c r="G13" s="64"/>
+      <c r="H13" s="64"/>
+      <c r="I13" s="64"/>
+      <c r="J13" s="62" t="str">
         <f>IF(Overview!$Q21=0,"ไม่มีรายการรอแก้ไข / No pending","มีรายการติดตามในชีตรายละเอียดจุดตรวจสอบ / See Station Details for follow-up")</f>
-        <v>ไม่มีรายการรอแก้ไข / No pending</v>
-      </c>
-      <c r="K13" s="65"/>
-      <c r="L13" s="65"/>
-      <c r="M13" s="65"/>
-      <c r="N13" s="65"/>
-      <c r="O13" s="65"/>
-      <c r="P13" s="65"/>
-      <c r="Q13" s="65"/>
+        <v>มีรายการติดตามในชีตรายละเอียดจุดตรวจสอบ / See Station Details for follow-up</v>
+      </c>
+      <c r="K13" s="62"/>
+      <c r="L13" s="62"/>
+      <c r="M13" s="62"/>
+      <c r="N13" s="62"/>
+      <c r="O13" s="62"/>
+      <c r="P13" s="62"/>
+      <c r="Q13" s="62"/>
     </row>
     <row r="14" spans="2:24" ht="25.2" customHeight="1">
       <c r="B14" s="43"/>
@@ -9597,16 +9600,6 @@
     <row r="336" ht="27" customHeight="1"/>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="B13:E13"/>
-    <mergeCell ref="F13:I13"/>
-    <mergeCell ref="J13:Q13"/>
-    <mergeCell ref="B9:Q9"/>
-    <mergeCell ref="B10:E10"/>
-    <mergeCell ref="F10:I10"/>
-    <mergeCell ref="J10:Q10"/>
-    <mergeCell ref="B11:E11"/>
-    <mergeCell ref="F11:I11"/>
-    <mergeCell ref="J11:Q11"/>
     <mergeCell ref="U1:W1"/>
     <mergeCell ref="D1:O1"/>
     <mergeCell ref="B2:Q2"/>
@@ -9623,6 +9616,16 @@
     <mergeCell ref="N6:Q6"/>
     <mergeCell ref="N7:Q7"/>
     <mergeCell ref="B5:Q5"/>
+    <mergeCell ref="B13:E13"/>
+    <mergeCell ref="F13:I13"/>
+    <mergeCell ref="J13:Q13"/>
+    <mergeCell ref="B9:Q9"/>
+    <mergeCell ref="B10:E10"/>
+    <mergeCell ref="F10:I10"/>
+    <mergeCell ref="J10:Q10"/>
+    <mergeCell ref="B11:E11"/>
+    <mergeCell ref="F11:I11"/>
+    <mergeCell ref="J11:Q11"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:B8">
     <cfRule type="duplicateValues" dxfId="8" priority="34"/>
@@ -9656,33 +9659,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="28.2" customHeight="1">
-      <c r="A1" s="68" t="s">
+      <c r="A1" s="72" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="68"/>
-      <c r="F1" s="68"/>
-      <c r="G1" s="68"/>
-      <c r="H1" s="68"/>
-      <c r="I1" s="68"/>
-      <c r="J1" s="68"/>
-      <c r="K1" s="68"/>
-      <c r="L1" s="68"/>
-      <c r="M1" s="68"/>
-      <c r="N1" s="68"/>
-      <c r="O1" s="68"/>
-      <c r="P1" s="68"/>
-      <c r="Q1" s="68"/>
-      <c r="R1" s="68"/>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="72"/>
+      <c r="G1" s="72"/>
+      <c r="H1" s="72"/>
+      <c r="I1" s="72"/>
+      <c r="J1" s="72"/>
+      <c r="K1" s="72"/>
+      <c r="L1" s="72"/>
+      <c r="M1" s="72"/>
+      <c r="N1" s="72"/>
+      <c r="O1" s="72"/>
+      <c r="P1" s="72"/>
+      <c r="Q1" s="72"/>
+      <c r="R1" s="72"/>
       <c r="T1" s="9" t="s">
         <v>17</v>
       </c>
       <c r="U1" s="9"/>
       <c r="V1" s="9"/>
-      <c r="W1" s="68"/>
-      <c r="X1" s="68"/>
+      <c r="W1" s="72"/>
+      <c r="X1" s="72"/>
       <c r="Y1" s="10"/>
     </row>
     <row r="2" spans="1:25" ht="25.95" customHeight="1">
@@ -10155,7 +10158,7 @@
       </c>
       <c r="U8" s="51">
         <f>COUNTBLANK(Q5:Q12)</f>
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:25" ht="21">
@@ -10166,7 +10169,7 @@
         <v>60</v>
       </c>
       <c r="C9" s="33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9" s="33" t="b">
         <v>0</v>
@@ -10178,7 +10181,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" s="33" t="b">
         <v>0</v>
@@ -10199,7 +10202,7 @@
         <v>0</v>
       </c>
       <c r="N9" s="33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O9" s="33" t="b">
         <v>0</v>
@@ -10207,9 +10210,9 @@
       <c r="P9" s="33" t="b">
         <v>0</v>
       </c>
-      <c r="Q9" s="25" t="str">
+      <c r="Q9" s="25">
         <f t="shared" si="1"/>
-        <v/>
+        <v>3</v>
       </c>
       <c r="R9" s="19"/>
       <c r="T9" s="49" t="s">
@@ -10217,7 +10220,7 @@
       </c>
       <c r="U9" s="52">
         <f>ROWS(Q5:Q12)-COUNTBLANK(Q5:Q12)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:25" ht="21">
@@ -10866,7 +10869,7 @@
       <c r="P21" s="24"/>
       <c r="Q21" s="26">
         <f>SUBTOTAL(2,Q5:Q20)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21" s="24"/>
     </row>
@@ -10956,7 +10959,7 @@
         <v>85</v>
       </c>
       <c r="F2" s="61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="24.6">
@@ -11196,7 +11199,7 @@
         <v>85</v>
       </c>
       <c r="F14" s="61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="24.6">
@@ -11356,7 +11359,7 @@
         <v>85</v>
       </c>
       <c r="F22" s="61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="24.6">
@@ -11476,7 +11479,7 @@
         <v>85</v>
       </c>
       <c r="F28" s="61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.6">
@@ -12136,7 +12139,7 @@
         <v>97</v>
       </c>
       <c r="F61" s="61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="24.6">
@@ -12156,7 +12159,7 @@
         <v>97</v>
       </c>
       <c r="F62" s="61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="24.6">
@@ -12496,7 +12499,7 @@
         <v>105</v>
       </c>
       <c r="F79" s="61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:6" ht="24.6">
@@ -12576,7 +12579,7 @@
         <v>105</v>
       </c>
       <c r="F83" s="61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:6" ht="24.6">
@@ -12596,7 +12599,7 @@
         <v>105</v>
       </c>
       <c r="F84" s="61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:6" ht="24.6">
@@ -12616,7 +12619,7 @@
         <v>105</v>
       </c>
       <c r="F85" s="61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86" spans="1:6" ht="24.6">
@@ -12916,7 +12919,7 @@
         <v>112</v>
       </c>
       <c r="F100" s="61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101" spans="1:6" ht="24.6">
@@ -13036,7 +13039,7 @@
         <v>112</v>
       </c>
       <c r="F106" s="61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107" spans="1:6" ht="24.6">
@@ -13416,7 +13419,7 @@
         <v>119</v>
       </c>
       <c r="F125" s="61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126" spans="1:6" ht="24.6">
@@ -13436,7 +13439,7 @@
         <v>119</v>
       </c>
       <c r="F126" s="61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127" spans="1:6" ht="24.6">
@@ -13476,7 +13479,7 @@
         <v>119</v>
       </c>
       <c r="F128" s="61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129" spans="1:6" ht="24.6">
@@ -13596,7 +13599,7 @@
         <v>124</v>
       </c>
       <c r="F134" s="61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135" spans="1:6" ht="24.6">
@@ -14196,7 +14199,7 @@
         <v>137</v>
       </c>
       <c r="F164" s="61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="165" spans="1:6" ht="24.6">
@@ -14436,7 +14439,7 @@
         <v>137</v>
       </c>
       <c r="F176" s="61" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="177" spans="1:6" ht="24.6">
@@ -14566,7 +14569,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{722C57DA-B53F-4EF5-81D4-89FE6AB9FDC7}">
-  <dimension ref="A1:E245"/>
+  <dimension ref="A1:E705"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="13.5" style="35" bestFit="1" customWidth="1"/>
@@ -17306,7 +17309,7 @@
         <v>46276</v>
       </c>
       <c r="C226" s="40">
-        <f t="shared" ref="C226:C245" si="5">IF(D226="",100,MAX(0,(1440-D226)/1440*100))</f>
+        <f t="shared" ref="C226:C289" si="5">IF(D226="",100,MAX(0,(1440-D226)/1440*100))</f>
         <v>100</v>
       </c>
     </row>
@@ -17535,6 +17538,5526 @@
       </c>
       <c r="C245" s="40">
         <f t="shared" si="5"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3">
+      <c r="A246" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B246" s="82">
+        <v>46296</v>
+      </c>
+      <c r="C246" s="40">
+        <f t="shared" si="5"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3">
+      <c r="A247" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B247" s="82">
+        <v>46297</v>
+      </c>
+      <c r="C247" s="40">
+        <f t="shared" si="5"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3">
+      <c r="A248" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B248" s="82">
+        <v>46298</v>
+      </c>
+      <c r="C248" s="40">
+        <f t="shared" si="5"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3">
+      <c r="A249" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B249" s="82">
+        <v>46299</v>
+      </c>
+      <c r="C249" s="40">
+        <f t="shared" si="5"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3">
+      <c r="A250" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B250" s="82">
+        <v>46300</v>
+      </c>
+      <c r="C250" s="40">
+        <f t="shared" si="5"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3">
+      <c r="A251" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B251" s="82">
+        <v>46301</v>
+      </c>
+      <c r="C251" s="40">
+        <f t="shared" si="5"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3">
+      <c r="A252" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B252" s="82">
+        <v>46302</v>
+      </c>
+      <c r="C252" s="40">
+        <f t="shared" si="5"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3">
+      <c r="A253" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B253" s="82">
+        <v>46303</v>
+      </c>
+      <c r="C253" s="40">
+        <f t="shared" si="5"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="254" spans="1:3">
+      <c r="A254" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B254" s="82">
+        <v>46304</v>
+      </c>
+      <c r="C254" s="40">
+        <f t="shared" si="5"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3">
+      <c r="A255" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B255" s="82">
+        <v>46305</v>
+      </c>
+      <c r="C255" s="40">
+        <f t="shared" si="5"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3">
+      <c r="A256" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B256" s="82">
+        <v>46306</v>
+      </c>
+      <c r="C256" s="40">
+        <f t="shared" si="5"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="257" spans="1:3">
+      <c r="A257" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B257" s="82">
+        <v>46307</v>
+      </c>
+      <c r="C257" s="40">
+        <f t="shared" si="5"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3">
+      <c r="A258" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B258" s="82">
+        <v>46308</v>
+      </c>
+      <c r="C258" s="40">
+        <f t="shared" si="5"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3">
+      <c r="A259" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B259" s="82">
+        <v>46309</v>
+      </c>
+      <c r="C259" s="40">
+        <f t="shared" si="5"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="260" spans="1:3">
+      <c r="A260" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B260" s="82">
+        <v>46310</v>
+      </c>
+      <c r="C260" s="40">
+        <f t="shared" si="5"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="261" spans="1:3">
+      <c r="A261" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B261" s="82">
+        <v>46311</v>
+      </c>
+      <c r="C261" s="40">
+        <f t="shared" si="5"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="262" spans="1:3">
+      <c r="A262" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B262" s="82">
+        <v>46312</v>
+      </c>
+      <c r="C262" s="40">
+        <f t="shared" si="5"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="263" spans="1:3">
+      <c r="A263" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B263" s="82">
+        <v>46313</v>
+      </c>
+      <c r="C263" s="40">
+        <f t="shared" si="5"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="264" spans="1:3">
+      <c r="A264" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B264" s="82">
+        <v>46314</v>
+      </c>
+      <c r="C264" s="40">
+        <f t="shared" si="5"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3">
+      <c r="A265" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B265" s="82">
+        <v>46315</v>
+      </c>
+      <c r="C265" s="40">
+        <f t="shared" si="5"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="266" spans="1:3">
+      <c r="A266" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B266" s="82">
+        <v>46316</v>
+      </c>
+      <c r="C266" s="40">
+        <f t="shared" si="5"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="267" spans="1:3">
+      <c r="A267" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B267" s="82">
+        <v>46317</v>
+      </c>
+      <c r="C267" s="40">
+        <f t="shared" si="5"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3">
+      <c r="A268" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B268" s="82">
+        <v>46318</v>
+      </c>
+      <c r="C268" s="40">
+        <f t="shared" si="5"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="269" spans="1:3">
+      <c r="A269" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B269" s="82">
+        <v>46319</v>
+      </c>
+      <c r="C269" s="40">
+        <f t="shared" si="5"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="270" spans="1:3">
+      <c r="A270" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B270" s="82">
+        <v>46320</v>
+      </c>
+      <c r="C270" s="40">
+        <f t="shared" si="5"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3">
+      <c r="A271" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B271" s="82">
+        <v>46321</v>
+      </c>
+      <c r="C271" s="40">
+        <f t="shared" si="5"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="272" spans="1:3">
+      <c r="A272" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B272" s="82">
+        <v>46322</v>
+      </c>
+      <c r="C272" s="40">
+        <f t="shared" si="5"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="273" spans="1:3">
+      <c r="A273" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B273" s="82">
+        <v>46323</v>
+      </c>
+      <c r="C273" s="40">
+        <f t="shared" si="5"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="274" spans="1:3">
+      <c r="A274" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B274" s="82">
+        <v>46324</v>
+      </c>
+      <c r="C274" s="40">
+        <f t="shared" si="5"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="275" spans="1:3">
+      <c r="A275" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B275" s="82">
+        <v>46325</v>
+      </c>
+      <c r="C275" s="40">
+        <f t="shared" si="5"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="276" spans="1:3">
+      <c r="A276" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B276" s="82">
+        <v>46326</v>
+      </c>
+      <c r="C276" s="40">
+        <f t="shared" si="5"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="277" spans="1:3">
+      <c r="A277" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B277" s="82">
+        <v>46327</v>
+      </c>
+      <c r="C277" s="40">
+        <f t="shared" si="5"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="278" spans="1:3">
+      <c r="A278" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B278" s="82">
+        <v>46328</v>
+      </c>
+      <c r="C278" s="40">
+        <f t="shared" si="5"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="279" spans="1:3">
+      <c r="A279" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B279" s="82">
+        <v>46329</v>
+      </c>
+      <c r="C279" s="40">
+        <f t="shared" si="5"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3">
+      <c r="A280" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B280" s="82">
+        <v>46330</v>
+      </c>
+      <c r="C280" s="40">
+        <f t="shared" si="5"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="281" spans="1:3">
+      <c r="A281" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B281" s="82">
+        <v>46331</v>
+      </c>
+      <c r="C281" s="40">
+        <f t="shared" si="5"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="282" spans="1:3">
+      <c r="A282" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B282" s="82">
+        <v>46332</v>
+      </c>
+      <c r="C282" s="40">
+        <f t="shared" si="5"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="283" spans="1:3">
+      <c r="A283" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B283" s="82">
+        <v>46333</v>
+      </c>
+      <c r="C283" s="40">
+        <f t="shared" si="5"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="284" spans="1:3">
+      <c r="A284" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B284" s="82">
+        <v>46334</v>
+      </c>
+      <c r="C284" s="40">
+        <f t="shared" si="5"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="285" spans="1:3">
+      <c r="A285" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B285" s="82">
+        <v>46335</v>
+      </c>
+      <c r="C285" s="40">
+        <f t="shared" si="5"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="286" spans="1:3">
+      <c r="A286" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B286" s="82">
+        <v>46336</v>
+      </c>
+      <c r="C286" s="40">
+        <f t="shared" si="5"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="287" spans="1:3">
+      <c r="A287" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B287" s="82">
+        <v>46337</v>
+      </c>
+      <c r="C287" s="40">
+        <f t="shared" si="5"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="288" spans="1:3">
+      <c r="A288" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B288" s="82">
+        <v>46338</v>
+      </c>
+      <c r="C288" s="40">
+        <f t="shared" si="5"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3">
+      <c r="A289" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B289" s="82">
+        <v>46339</v>
+      </c>
+      <c r="C289" s="40">
+        <f t="shared" si="5"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="290" spans="1:3">
+      <c r="A290" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B290" s="82">
+        <v>46340</v>
+      </c>
+      <c r="C290" s="40">
+        <f t="shared" ref="C290:C353" si="6">IF(D290="",100,MAX(0,(1440-D290)/1440*100))</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="291" spans="1:3">
+      <c r="A291" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B291" s="82">
+        <v>46341</v>
+      </c>
+      <c r="C291" s="40">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="292" spans="1:3">
+      <c r="A292" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B292" s="82">
+        <v>46342</v>
+      </c>
+      <c r="C292" s="40">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="293" spans="1:3">
+      <c r="A293" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B293" s="82">
+        <v>46343</v>
+      </c>
+      <c r="C293" s="40">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="294" spans="1:3">
+      <c r="A294" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B294" s="82">
+        <v>46344</v>
+      </c>
+      <c r="C294" s="40">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="295" spans="1:3">
+      <c r="A295" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B295" s="82">
+        <v>46345</v>
+      </c>
+      <c r="C295" s="40">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="296" spans="1:3">
+      <c r="A296" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B296" s="82">
+        <v>46346</v>
+      </c>
+      <c r="C296" s="40">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="297" spans="1:3">
+      <c r="A297" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B297" s="82">
+        <v>46347</v>
+      </c>
+      <c r="C297" s="40">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="298" spans="1:3">
+      <c r="A298" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B298" s="82">
+        <v>46348</v>
+      </c>
+      <c r="C298" s="40">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="299" spans="1:3">
+      <c r="A299" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B299" s="82">
+        <v>46349</v>
+      </c>
+      <c r="C299" s="40">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="300" spans="1:3">
+      <c r="A300" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B300" s="82">
+        <v>46350</v>
+      </c>
+      <c r="C300" s="40">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="301" spans="1:3">
+      <c r="A301" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B301" s="82">
+        <v>46351</v>
+      </c>
+      <c r="C301" s="40">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="302" spans="1:3">
+      <c r="A302" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B302" s="82">
+        <v>46352</v>
+      </c>
+      <c r="C302" s="40">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="303" spans="1:3">
+      <c r="A303" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B303" s="82">
+        <v>46353</v>
+      </c>
+      <c r="C303" s="40">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="304" spans="1:3">
+      <c r="A304" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B304" s="82">
+        <v>46354</v>
+      </c>
+      <c r="C304" s="40">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="305" spans="1:3">
+      <c r="A305" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B305" s="82">
+        <v>46355</v>
+      </c>
+      <c r="C305" s="40">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="306" spans="1:3">
+      <c r="A306" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B306" s="82">
+        <v>46356</v>
+      </c>
+      <c r="C306" s="40">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="307" spans="1:3">
+      <c r="A307" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B307" s="82">
+        <v>46357</v>
+      </c>
+      <c r="C307" s="40">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="308" spans="1:3">
+      <c r="A308" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B308" s="82">
+        <v>46358</v>
+      </c>
+      <c r="C308" s="40">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="309" spans="1:3">
+      <c r="A309" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B309" s="82">
+        <v>46359</v>
+      </c>
+      <c r="C309" s="40">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="310" spans="1:3">
+      <c r="A310" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B310" s="82">
+        <v>46360</v>
+      </c>
+      <c r="C310" s="40">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="311" spans="1:3">
+      <c r="A311" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B311" s="82">
+        <v>46361</v>
+      </c>
+      <c r="C311" s="40">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="312" spans="1:3">
+      <c r="A312" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B312" s="82">
+        <v>46362</v>
+      </c>
+      <c r="C312" s="40">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="313" spans="1:3">
+      <c r="A313" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B313" s="82">
+        <v>46363</v>
+      </c>
+      <c r="C313" s="40">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="314" spans="1:3">
+      <c r="A314" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B314" s="82">
+        <v>46364</v>
+      </c>
+      <c r="C314" s="40">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="315" spans="1:3">
+      <c r="A315" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B315" s="82">
+        <v>46365</v>
+      </c>
+      <c r="C315" s="40">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="316" spans="1:3">
+      <c r="A316" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B316" s="82">
+        <v>46366</v>
+      </c>
+      <c r="C316" s="40">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="317" spans="1:3">
+      <c r="A317" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B317" s="82">
+        <v>46367</v>
+      </c>
+      <c r="C317" s="40">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="318" spans="1:3">
+      <c r="A318" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B318" s="82">
+        <v>46368</v>
+      </c>
+      <c r="C318" s="40">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="319" spans="1:3">
+      <c r="A319" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B319" s="82">
+        <v>46369</v>
+      </c>
+      <c r="C319" s="40">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="320" spans="1:3">
+      <c r="A320" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B320" s="82">
+        <v>46370</v>
+      </c>
+      <c r="C320" s="40">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="321" spans="1:3">
+      <c r="A321" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B321" s="82">
+        <v>46371</v>
+      </c>
+      <c r="C321" s="40">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="322" spans="1:3">
+      <c r="A322" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B322" s="82">
+        <v>46372</v>
+      </c>
+      <c r="C322" s="40">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="323" spans="1:3">
+      <c r="A323" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B323" s="82">
+        <v>46373</v>
+      </c>
+      <c r="C323" s="40">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="324" spans="1:3">
+      <c r="A324" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B324" s="82">
+        <v>46374</v>
+      </c>
+      <c r="C324" s="40">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="325" spans="1:3">
+      <c r="A325" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B325" s="82">
+        <v>46375</v>
+      </c>
+      <c r="C325" s="40">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="326" spans="1:3">
+      <c r="A326" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B326" s="82">
+        <v>46376</v>
+      </c>
+      <c r="C326" s="40">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="327" spans="1:3">
+      <c r="A327" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B327" s="82">
+        <v>46377</v>
+      </c>
+      <c r="C327" s="40">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="328" spans="1:3">
+      <c r="A328" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B328" s="82">
+        <v>46378</v>
+      </c>
+      <c r="C328" s="40">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="329" spans="1:3">
+      <c r="A329" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B329" s="82">
+        <v>46379</v>
+      </c>
+      <c r="C329" s="40">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="330" spans="1:3">
+      <c r="A330" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B330" s="82">
+        <v>46380</v>
+      </c>
+      <c r="C330" s="40">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="331" spans="1:3">
+      <c r="A331" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B331" s="82">
+        <v>46381</v>
+      </c>
+      <c r="C331" s="40">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="332" spans="1:3">
+      <c r="A332" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B332" s="82">
+        <v>46382</v>
+      </c>
+      <c r="C332" s="40">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="333" spans="1:3">
+      <c r="A333" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B333" s="82">
+        <v>46383</v>
+      </c>
+      <c r="C333" s="40">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="334" spans="1:3">
+      <c r="A334" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B334" s="82">
+        <v>46384</v>
+      </c>
+      <c r="C334" s="40">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="335" spans="1:3">
+      <c r="A335" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B335" s="82">
+        <v>46385</v>
+      </c>
+      <c r="C335" s="40">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="336" spans="1:3">
+      <c r="A336" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B336" s="82">
+        <v>46386</v>
+      </c>
+      <c r="C336" s="40">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="337" spans="1:3">
+      <c r="A337" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B337" s="82">
+        <v>46387</v>
+      </c>
+      <c r="C337" s="40">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="338" spans="1:3">
+      <c r="A338" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B338" s="82">
+        <v>46296</v>
+      </c>
+      <c r="C338" s="40">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="339" spans="1:3">
+      <c r="A339" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B339" s="82">
+        <v>46297</v>
+      </c>
+      <c r="C339" s="40">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="340" spans="1:3">
+      <c r="A340" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B340" s="82">
+        <v>46298</v>
+      </c>
+      <c r="C340" s="40">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="341" spans="1:3">
+      <c r="A341" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B341" s="82">
+        <v>46299</v>
+      </c>
+      <c r="C341" s="40">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="342" spans="1:3">
+      <c r="A342" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B342" s="82">
+        <v>46300</v>
+      </c>
+      <c r="C342" s="40">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="343" spans="1:3">
+      <c r="A343" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B343" s="82">
+        <v>46301</v>
+      </c>
+      <c r="C343" s="40">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="344" spans="1:3">
+      <c r="A344" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B344" s="82">
+        <v>46302</v>
+      </c>
+      <c r="C344" s="40">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="345" spans="1:3">
+      <c r="A345" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B345" s="82">
+        <v>46303</v>
+      </c>
+      <c r="C345" s="40">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="346" spans="1:3">
+      <c r="A346" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B346" s="82">
+        <v>46304</v>
+      </c>
+      <c r="C346" s="40">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="347" spans="1:3">
+      <c r="A347" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B347" s="82">
+        <v>46305</v>
+      </c>
+      <c r="C347" s="40">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="348" spans="1:3">
+      <c r="A348" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B348" s="82">
+        <v>46306</v>
+      </c>
+      <c r="C348" s="40">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="349" spans="1:3">
+      <c r="A349" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B349" s="82">
+        <v>46307</v>
+      </c>
+      <c r="C349" s="40">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="350" spans="1:3">
+      <c r="A350" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B350" s="82">
+        <v>46308</v>
+      </c>
+      <c r="C350" s="40">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="351" spans="1:3">
+      <c r="A351" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B351" s="82">
+        <v>46309</v>
+      </c>
+      <c r="C351" s="40">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="352" spans="1:3">
+      <c r="A352" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B352" s="82">
+        <v>46310</v>
+      </c>
+      <c r="C352" s="40">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="353" spans="1:3">
+      <c r="A353" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B353" s="82">
+        <v>46311</v>
+      </c>
+      <c r="C353" s="40">
+        <f t="shared" si="6"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="354" spans="1:3">
+      <c r="A354" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B354" s="82">
+        <v>46312</v>
+      </c>
+      <c r="C354" s="40">
+        <f t="shared" ref="C354:C417" si="7">IF(D354="",100,MAX(0,(1440-D354)/1440*100))</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="355" spans="1:3">
+      <c r="A355" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B355" s="82">
+        <v>46313</v>
+      </c>
+      <c r="C355" s="40">
+        <f t="shared" si="7"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="356" spans="1:3">
+      <c r="A356" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B356" s="82">
+        <v>46314</v>
+      </c>
+      <c r="C356" s="40">
+        <f t="shared" si="7"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="357" spans="1:3">
+      <c r="A357" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B357" s="82">
+        <v>46315</v>
+      </c>
+      <c r="C357" s="40">
+        <f t="shared" si="7"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="358" spans="1:3">
+      <c r="A358" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B358" s="82">
+        <v>46316</v>
+      </c>
+      <c r="C358" s="40">
+        <f t="shared" si="7"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="359" spans="1:3">
+      <c r="A359" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B359" s="82">
+        <v>46317</v>
+      </c>
+      <c r="C359" s="40">
+        <f t="shared" si="7"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="360" spans="1:3">
+      <c r="A360" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B360" s="82">
+        <v>46318</v>
+      </c>
+      <c r="C360" s="40">
+        <f t="shared" si="7"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="361" spans="1:3">
+      <c r="A361" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B361" s="82">
+        <v>46319</v>
+      </c>
+      <c r="C361" s="40">
+        <f t="shared" si="7"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="362" spans="1:3">
+      <c r="A362" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B362" s="82">
+        <v>46320</v>
+      </c>
+      <c r="C362" s="40">
+        <f t="shared" si="7"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="363" spans="1:3">
+      <c r="A363" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B363" s="82">
+        <v>46321</v>
+      </c>
+      <c r="C363" s="40">
+        <f t="shared" si="7"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="364" spans="1:3">
+      <c r="A364" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B364" s="82">
+        <v>46322</v>
+      </c>
+      <c r="C364" s="40">
+        <f t="shared" si="7"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="365" spans="1:3">
+      <c r="A365" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B365" s="82">
+        <v>46323</v>
+      </c>
+      <c r="C365" s="40">
+        <f t="shared" si="7"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="366" spans="1:3">
+      <c r="A366" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B366" s="82">
+        <v>46324</v>
+      </c>
+      <c r="C366" s="40">
+        <f t="shared" si="7"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="367" spans="1:3">
+      <c r="A367" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B367" s="82">
+        <v>46325</v>
+      </c>
+      <c r="C367" s="40">
+        <f t="shared" si="7"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="368" spans="1:3">
+      <c r="A368" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B368" s="82">
+        <v>46326</v>
+      </c>
+      <c r="C368" s="40">
+        <f t="shared" si="7"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="369" spans="1:3">
+      <c r="A369" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B369" s="82">
+        <v>46327</v>
+      </c>
+      <c r="C369" s="40">
+        <f t="shared" si="7"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="370" spans="1:3">
+      <c r="A370" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B370" s="82">
+        <v>46328</v>
+      </c>
+      <c r="C370" s="40">
+        <f t="shared" si="7"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="371" spans="1:3">
+      <c r="A371" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B371" s="82">
+        <v>46329</v>
+      </c>
+      <c r="C371" s="40">
+        <f t="shared" si="7"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="372" spans="1:3">
+      <c r="A372" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B372" s="82">
+        <v>46330</v>
+      </c>
+      <c r="C372" s="40">
+        <f t="shared" si="7"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="373" spans="1:3">
+      <c r="A373" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B373" s="82">
+        <v>46331</v>
+      </c>
+      <c r="C373" s="40">
+        <f t="shared" si="7"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="374" spans="1:3">
+      <c r="A374" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B374" s="82">
+        <v>46332</v>
+      </c>
+      <c r="C374" s="40">
+        <f t="shared" si="7"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="375" spans="1:3">
+      <c r="A375" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B375" s="82">
+        <v>46333</v>
+      </c>
+      <c r="C375" s="40">
+        <f t="shared" si="7"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="376" spans="1:3">
+      <c r="A376" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B376" s="82">
+        <v>46334</v>
+      </c>
+      <c r="C376" s="40">
+        <f t="shared" si="7"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="377" spans="1:3">
+      <c r="A377" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B377" s="82">
+        <v>46335</v>
+      </c>
+      <c r="C377" s="40">
+        <f t="shared" si="7"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="378" spans="1:3">
+      <c r="A378" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B378" s="82">
+        <v>46336</v>
+      </c>
+      <c r="C378" s="40">
+        <f t="shared" si="7"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="379" spans="1:3">
+      <c r="A379" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B379" s="82">
+        <v>46337</v>
+      </c>
+      <c r="C379" s="40">
+        <f t="shared" si="7"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="380" spans="1:3">
+      <c r="A380" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B380" s="82">
+        <v>46338</v>
+      </c>
+      <c r="C380" s="40">
+        <f t="shared" si="7"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="381" spans="1:3">
+      <c r="A381" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B381" s="82">
+        <v>46339</v>
+      </c>
+      <c r="C381" s="40">
+        <f t="shared" si="7"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="382" spans="1:3">
+      <c r="A382" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B382" s="82">
+        <v>46340</v>
+      </c>
+      <c r="C382" s="40">
+        <f t="shared" si="7"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="383" spans="1:3">
+      <c r="A383" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B383" s="82">
+        <v>46341</v>
+      </c>
+      <c r="C383" s="40">
+        <f t="shared" si="7"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="384" spans="1:3">
+      <c r="A384" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B384" s="82">
+        <v>46342</v>
+      </c>
+      <c r="C384" s="40">
+        <f t="shared" si="7"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="385" spans="1:3">
+      <c r="A385" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B385" s="82">
+        <v>46343</v>
+      </c>
+      <c r="C385" s="40">
+        <f t="shared" si="7"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="386" spans="1:3">
+      <c r="A386" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B386" s="82">
+        <v>46344</v>
+      </c>
+      <c r="C386" s="40">
+        <f t="shared" si="7"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="387" spans="1:3">
+      <c r="A387" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B387" s="82">
+        <v>46345</v>
+      </c>
+      <c r="C387" s="40">
+        <f t="shared" si="7"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="388" spans="1:3">
+      <c r="A388" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B388" s="82">
+        <v>46346</v>
+      </c>
+      <c r="C388" s="40">
+        <f t="shared" si="7"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="389" spans="1:3">
+      <c r="A389" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B389" s="82">
+        <v>46347</v>
+      </c>
+      <c r="C389" s="40">
+        <f t="shared" si="7"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="390" spans="1:3">
+      <c r="A390" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B390" s="82">
+        <v>46348</v>
+      </c>
+      <c r="C390" s="40">
+        <f t="shared" si="7"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="391" spans="1:3">
+      <c r="A391" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B391" s="82">
+        <v>46349</v>
+      </c>
+      <c r="C391" s="40">
+        <f t="shared" si="7"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="392" spans="1:3">
+      <c r="A392" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B392" s="82">
+        <v>46350</v>
+      </c>
+      <c r="C392" s="40">
+        <f t="shared" si="7"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="393" spans="1:3">
+      <c r="A393" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B393" s="82">
+        <v>46351</v>
+      </c>
+      <c r="C393" s="40">
+        <f t="shared" si="7"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="394" spans="1:3">
+      <c r="A394" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B394" s="82">
+        <v>46352</v>
+      </c>
+      <c r="C394" s="40">
+        <f t="shared" si="7"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="395" spans="1:3">
+      <c r="A395" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B395" s="82">
+        <v>46353</v>
+      </c>
+      <c r="C395" s="40">
+        <f t="shared" si="7"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="396" spans="1:3">
+      <c r="A396" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B396" s="82">
+        <v>46354</v>
+      </c>
+      <c r="C396" s="40">
+        <f t="shared" si="7"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="397" spans="1:3">
+      <c r="A397" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B397" s="82">
+        <v>46355</v>
+      </c>
+      <c r="C397" s="40">
+        <f t="shared" si="7"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="398" spans="1:3">
+      <c r="A398" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B398" s="82">
+        <v>46356</v>
+      </c>
+      <c r="C398" s="40">
+        <f t="shared" si="7"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="399" spans="1:3">
+      <c r="A399" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B399" s="82">
+        <v>46357</v>
+      </c>
+      <c r="C399" s="40">
+        <f t="shared" si="7"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="400" spans="1:3">
+      <c r="A400" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B400" s="82">
+        <v>46358</v>
+      </c>
+      <c r="C400" s="40">
+        <f t="shared" si="7"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="401" spans="1:3">
+      <c r="A401" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B401" s="82">
+        <v>46359</v>
+      </c>
+      <c r="C401" s="40">
+        <f t="shared" si="7"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="402" spans="1:3">
+      <c r="A402" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B402" s="82">
+        <v>46360</v>
+      </c>
+      <c r="C402" s="40">
+        <f t="shared" si="7"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="403" spans="1:3">
+      <c r="A403" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B403" s="82">
+        <v>46361</v>
+      </c>
+      <c r="C403" s="40">
+        <f t="shared" si="7"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="404" spans="1:3">
+      <c r="A404" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B404" s="82">
+        <v>46362</v>
+      </c>
+      <c r="C404" s="40">
+        <f t="shared" si="7"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="405" spans="1:3">
+      <c r="A405" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B405" s="82">
+        <v>46363</v>
+      </c>
+      <c r="C405" s="40">
+        <f t="shared" si="7"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="406" spans="1:3">
+      <c r="A406" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B406" s="82">
+        <v>46364</v>
+      </c>
+      <c r="C406" s="40">
+        <f t="shared" si="7"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="407" spans="1:3">
+      <c r="A407" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B407" s="82">
+        <v>46365</v>
+      </c>
+      <c r="C407" s="40">
+        <f t="shared" si="7"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="408" spans="1:3">
+      <c r="A408" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B408" s="82">
+        <v>46366</v>
+      </c>
+      <c r="C408" s="40">
+        <f t="shared" si="7"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="409" spans="1:3">
+      <c r="A409" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B409" s="82">
+        <v>46367</v>
+      </c>
+      <c r="C409" s="40">
+        <f t="shared" si="7"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="410" spans="1:3">
+      <c r="A410" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B410" s="82">
+        <v>46368</v>
+      </c>
+      <c r="C410" s="40">
+        <f t="shared" si="7"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="411" spans="1:3">
+      <c r="A411" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B411" s="82">
+        <v>46369</v>
+      </c>
+      <c r="C411" s="40">
+        <f t="shared" si="7"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="412" spans="1:3">
+      <c r="A412" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B412" s="82">
+        <v>46370</v>
+      </c>
+      <c r="C412" s="40">
+        <f t="shared" si="7"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="413" spans="1:3">
+      <c r="A413" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B413" s="82">
+        <v>46371</v>
+      </c>
+      <c r="C413" s="40">
+        <f t="shared" si="7"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="414" spans="1:3">
+      <c r="A414" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B414" s="82">
+        <v>46372</v>
+      </c>
+      <c r="C414" s="40">
+        <f t="shared" si="7"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="415" spans="1:3">
+      <c r="A415" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B415" s="82">
+        <v>46373</v>
+      </c>
+      <c r="C415" s="40">
+        <f t="shared" si="7"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="416" spans="1:3">
+      <c r="A416" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B416" s="82">
+        <v>46374</v>
+      </c>
+      <c r="C416" s="40">
+        <f t="shared" si="7"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="417" spans="1:3">
+      <c r="A417" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B417" s="82">
+        <v>46375</v>
+      </c>
+      <c r="C417" s="40">
+        <f t="shared" si="7"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="418" spans="1:3">
+      <c r="A418" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B418" s="82">
+        <v>46376</v>
+      </c>
+      <c r="C418" s="40">
+        <f t="shared" ref="C418:C481" si="8">IF(D418="",100,MAX(0,(1440-D418)/1440*100))</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="419" spans="1:3">
+      <c r="A419" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B419" s="82">
+        <v>46377</v>
+      </c>
+      <c r="C419" s="40">
+        <f t="shared" si="8"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="420" spans="1:3">
+      <c r="A420" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B420" s="82">
+        <v>46378</v>
+      </c>
+      <c r="C420" s="40">
+        <f t="shared" si="8"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="421" spans="1:3">
+      <c r="A421" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B421" s="82">
+        <v>46379</v>
+      </c>
+      <c r="C421" s="40">
+        <f t="shared" si="8"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="422" spans="1:3">
+      <c r="A422" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B422" s="82">
+        <v>46380</v>
+      </c>
+      <c r="C422" s="40">
+        <f t="shared" si="8"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="423" spans="1:3">
+      <c r="A423" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B423" s="82">
+        <v>46381</v>
+      </c>
+      <c r="C423" s="40">
+        <f t="shared" si="8"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="424" spans="1:3">
+      <c r="A424" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B424" s="82">
+        <v>46382</v>
+      </c>
+      <c r="C424" s="40">
+        <f t="shared" si="8"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="425" spans="1:3">
+      <c r="A425" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B425" s="82">
+        <v>46383</v>
+      </c>
+      <c r="C425" s="40">
+        <f t="shared" si="8"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="426" spans="1:3">
+      <c r="A426" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B426" s="82">
+        <v>46384</v>
+      </c>
+      <c r="C426" s="40">
+        <f t="shared" si="8"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="427" spans="1:3">
+      <c r="A427" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B427" s="82">
+        <v>46385</v>
+      </c>
+      <c r="C427" s="40">
+        <f t="shared" si="8"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="428" spans="1:3">
+      <c r="A428" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B428" s="82">
+        <v>46386</v>
+      </c>
+      <c r="C428" s="40">
+        <f t="shared" si="8"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="429" spans="1:3">
+      <c r="A429" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B429" s="82">
+        <v>46387</v>
+      </c>
+      <c r="C429" s="40">
+        <f t="shared" si="8"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="430" spans="1:3">
+      <c r="A430" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B430" s="82">
+        <v>46296</v>
+      </c>
+      <c r="C430" s="40">
+        <f t="shared" si="8"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="431" spans="1:3">
+      <c r="A431" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B431" s="82">
+        <v>46297</v>
+      </c>
+      <c r="C431" s="40">
+        <f t="shared" si="8"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="432" spans="1:3">
+      <c r="A432" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B432" s="82">
+        <v>46298</v>
+      </c>
+      <c r="C432" s="40">
+        <f t="shared" si="8"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="433" spans="1:3">
+      <c r="A433" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B433" s="82">
+        <v>46299</v>
+      </c>
+      <c r="C433" s="40">
+        <f t="shared" si="8"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="434" spans="1:3">
+      <c r="A434" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B434" s="82">
+        <v>46300</v>
+      </c>
+      <c r="C434" s="40">
+        <f t="shared" si="8"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="435" spans="1:3">
+      <c r="A435" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B435" s="82">
+        <v>46301</v>
+      </c>
+      <c r="C435" s="40">
+        <f t="shared" si="8"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="436" spans="1:3">
+      <c r="A436" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B436" s="82">
+        <v>46302</v>
+      </c>
+      <c r="C436" s="40">
+        <f t="shared" si="8"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="437" spans="1:3">
+      <c r="A437" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B437" s="82">
+        <v>46303</v>
+      </c>
+      <c r="C437" s="40">
+        <f t="shared" si="8"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="438" spans="1:3">
+      <c r="A438" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B438" s="82">
+        <v>46304</v>
+      </c>
+      <c r="C438" s="40">
+        <f t="shared" si="8"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="439" spans="1:3">
+      <c r="A439" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B439" s="82">
+        <v>46305</v>
+      </c>
+      <c r="C439" s="40">
+        <f t="shared" si="8"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="440" spans="1:3">
+      <c r="A440" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B440" s="82">
+        <v>46306</v>
+      </c>
+      <c r="C440" s="40">
+        <f t="shared" si="8"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="441" spans="1:3">
+      <c r="A441" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B441" s="82">
+        <v>46307</v>
+      </c>
+      <c r="C441" s="40">
+        <f t="shared" si="8"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="442" spans="1:3">
+      <c r="A442" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B442" s="82">
+        <v>46308</v>
+      </c>
+      <c r="C442" s="40">
+        <f t="shared" si="8"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="443" spans="1:3">
+      <c r="A443" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B443" s="82">
+        <v>46309</v>
+      </c>
+      <c r="C443" s="40">
+        <f t="shared" si="8"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="444" spans="1:3">
+      <c r="A444" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B444" s="82">
+        <v>46310</v>
+      </c>
+      <c r="C444" s="40">
+        <f t="shared" si="8"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="445" spans="1:3">
+      <c r="A445" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B445" s="82">
+        <v>46311</v>
+      </c>
+      <c r="C445" s="40">
+        <f t="shared" si="8"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="446" spans="1:3">
+      <c r="A446" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B446" s="82">
+        <v>46312</v>
+      </c>
+      <c r="C446" s="40">
+        <f t="shared" si="8"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="447" spans="1:3">
+      <c r="A447" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B447" s="82">
+        <v>46313</v>
+      </c>
+      <c r="C447" s="40">
+        <f t="shared" si="8"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="448" spans="1:3">
+      <c r="A448" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B448" s="82">
+        <v>46314</v>
+      </c>
+      <c r="C448" s="40">
+        <f t="shared" si="8"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="449" spans="1:3">
+      <c r="A449" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B449" s="82">
+        <v>46315</v>
+      </c>
+      <c r="C449" s="40">
+        <f t="shared" si="8"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="450" spans="1:3">
+      <c r="A450" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B450" s="82">
+        <v>46316</v>
+      </c>
+      <c r="C450" s="40">
+        <f t="shared" si="8"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="451" spans="1:3">
+      <c r="A451" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B451" s="82">
+        <v>46317</v>
+      </c>
+      <c r="C451" s="40">
+        <f t="shared" si="8"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="452" spans="1:3">
+      <c r="A452" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B452" s="82">
+        <v>46318</v>
+      </c>
+      <c r="C452" s="40">
+        <f t="shared" si="8"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="453" spans="1:3">
+      <c r="A453" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B453" s="82">
+        <v>46319</v>
+      </c>
+      <c r="C453" s="40">
+        <f t="shared" si="8"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="454" spans="1:3">
+      <c r="A454" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B454" s="82">
+        <v>46320</v>
+      </c>
+      <c r="C454" s="40">
+        <f t="shared" si="8"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="455" spans="1:3">
+      <c r="A455" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B455" s="82">
+        <v>46321</v>
+      </c>
+      <c r="C455" s="40">
+        <f t="shared" si="8"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="456" spans="1:3">
+      <c r="A456" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B456" s="82">
+        <v>46322</v>
+      </c>
+      <c r="C456" s="40">
+        <f t="shared" si="8"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="457" spans="1:3">
+      <c r="A457" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B457" s="82">
+        <v>46323</v>
+      </c>
+      <c r="C457" s="40">
+        <f t="shared" si="8"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="458" spans="1:3">
+      <c r="A458" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B458" s="82">
+        <v>46324</v>
+      </c>
+      <c r="C458" s="40">
+        <f t="shared" si="8"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="459" spans="1:3">
+      <c r="A459" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B459" s="82">
+        <v>46325</v>
+      </c>
+      <c r="C459" s="40">
+        <f t="shared" si="8"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="460" spans="1:3">
+      <c r="A460" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B460" s="82">
+        <v>46326</v>
+      </c>
+      <c r="C460" s="40">
+        <f t="shared" si="8"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="461" spans="1:3">
+      <c r="A461" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B461" s="82">
+        <v>46327</v>
+      </c>
+      <c r="C461" s="40">
+        <f t="shared" si="8"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="462" spans="1:3">
+      <c r="A462" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B462" s="82">
+        <v>46328</v>
+      </c>
+      <c r="C462" s="40">
+        <f t="shared" si="8"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="463" spans="1:3">
+      <c r="A463" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B463" s="82">
+        <v>46329</v>
+      </c>
+      <c r="C463" s="40">
+        <f t="shared" si="8"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="464" spans="1:3">
+      <c r="A464" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B464" s="82">
+        <v>46330</v>
+      </c>
+      <c r="C464" s="40">
+        <f t="shared" si="8"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="465" spans="1:3">
+      <c r="A465" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B465" s="82">
+        <v>46331</v>
+      </c>
+      <c r="C465" s="40">
+        <f t="shared" si="8"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="466" spans="1:3">
+      <c r="A466" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B466" s="82">
+        <v>46332</v>
+      </c>
+      <c r="C466" s="40">
+        <f t="shared" si="8"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="467" spans="1:3">
+      <c r="A467" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B467" s="82">
+        <v>46333</v>
+      </c>
+      <c r="C467" s="40">
+        <f t="shared" si="8"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="468" spans="1:3">
+      <c r="A468" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B468" s="82">
+        <v>46334</v>
+      </c>
+      <c r="C468" s="40">
+        <f t="shared" si="8"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="469" spans="1:3">
+      <c r="A469" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B469" s="82">
+        <v>46335</v>
+      </c>
+      <c r="C469" s="40">
+        <f t="shared" si="8"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="470" spans="1:3">
+      <c r="A470" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B470" s="82">
+        <v>46336</v>
+      </c>
+      <c r="C470" s="40">
+        <f t="shared" si="8"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="471" spans="1:3">
+      <c r="A471" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B471" s="82">
+        <v>46337</v>
+      </c>
+      <c r="C471" s="40">
+        <f t="shared" si="8"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="472" spans="1:3">
+      <c r="A472" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B472" s="82">
+        <v>46338</v>
+      </c>
+      <c r="C472" s="40">
+        <f t="shared" si="8"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="473" spans="1:3">
+      <c r="A473" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B473" s="82">
+        <v>46339</v>
+      </c>
+      <c r="C473" s="40">
+        <f t="shared" si="8"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="474" spans="1:3">
+      <c r="A474" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B474" s="82">
+        <v>46340</v>
+      </c>
+      <c r="C474" s="40">
+        <f t="shared" si="8"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="475" spans="1:3">
+      <c r="A475" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B475" s="82">
+        <v>46341</v>
+      </c>
+      <c r="C475" s="40">
+        <f t="shared" si="8"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="476" spans="1:3">
+      <c r="A476" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B476" s="82">
+        <v>46342</v>
+      </c>
+      <c r="C476" s="40">
+        <f t="shared" si="8"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="477" spans="1:3">
+      <c r="A477" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B477" s="82">
+        <v>46343</v>
+      </c>
+      <c r="C477" s="40">
+        <f t="shared" si="8"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="478" spans="1:3">
+      <c r="A478" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B478" s="82">
+        <v>46344</v>
+      </c>
+      <c r="C478" s="40">
+        <f t="shared" si="8"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="479" spans="1:3">
+      <c r="A479" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B479" s="82">
+        <v>46345</v>
+      </c>
+      <c r="C479" s="40">
+        <f t="shared" si="8"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="480" spans="1:3">
+      <c r="A480" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B480" s="82">
+        <v>46346</v>
+      </c>
+      <c r="C480" s="40">
+        <f t="shared" si="8"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="481" spans="1:3">
+      <c r="A481" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B481" s="82">
+        <v>46347</v>
+      </c>
+      <c r="C481" s="40">
+        <f t="shared" si="8"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="482" spans="1:3">
+      <c r="A482" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B482" s="82">
+        <v>46348</v>
+      </c>
+      <c r="C482" s="40">
+        <f t="shared" ref="C482:C545" si="9">IF(D482="",100,MAX(0,(1440-D482)/1440*100))</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="483" spans="1:3">
+      <c r="A483" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B483" s="82">
+        <v>46349</v>
+      </c>
+      <c r="C483" s="40">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="484" spans="1:3">
+      <c r="A484" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B484" s="82">
+        <v>46350</v>
+      </c>
+      <c r="C484" s="40">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="485" spans="1:3">
+      <c r="A485" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B485" s="82">
+        <v>46351</v>
+      </c>
+      <c r="C485" s="40">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="486" spans="1:3">
+      <c r="A486" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B486" s="82">
+        <v>46352</v>
+      </c>
+      <c r="C486" s="40">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="487" spans="1:3">
+      <c r="A487" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B487" s="82">
+        <v>46353</v>
+      </c>
+      <c r="C487" s="40">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="488" spans="1:3">
+      <c r="A488" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B488" s="82">
+        <v>46354</v>
+      </c>
+      <c r="C488" s="40">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="489" spans="1:3">
+      <c r="A489" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B489" s="82">
+        <v>46355</v>
+      </c>
+      <c r="C489" s="40">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="490" spans="1:3">
+      <c r="A490" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B490" s="82">
+        <v>46356</v>
+      </c>
+      <c r="C490" s="40">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="491" spans="1:3">
+      <c r="A491" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B491" s="82">
+        <v>46357</v>
+      </c>
+      <c r="C491" s="40">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="492" spans="1:3">
+      <c r="A492" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B492" s="82">
+        <v>46358</v>
+      </c>
+      <c r="C492" s="40">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="493" spans="1:3">
+      <c r="A493" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B493" s="82">
+        <v>46359</v>
+      </c>
+      <c r="C493" s="40">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="494" spans="1:3">
+      <c r="A494" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B494" s="82">
+        <v>46360</v>
+      </c>
+      <c r="C494" s="40">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="495" spans="1:3">
+      <c r="A495" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B495" s="82">
+        <v>46361</v>
+      </c>
+      <c r="C495" s="40">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="496" spans="1:3">
+      <c r="A496" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B496" s="82">
+        <v>46362</v>
+      </c>
+      <c r="C496" s="40">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="497" spans="1:3">
+      <c r="A497" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B497" s="82">
+        <v>46363</v>
+      </c>
+      <c r="C497" s="40">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="498" spans="1:3">
+      <c r="A498" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B498" s="82">
+        <v>46364</v>
+      </c>
+      <c r="C498" s="40">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="499" spans="1:3">
+      <c r="A499" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B499" s="82">
+        <v>46365</v>
+      </c>
+      <c r="C499" s="40">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="500" spans="1:3">
+      <c r="A500" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B500" s="82">
+        <v>46366</v>
+      </c>
+      <c r="C500" s="40">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="501" spans="1:3">
+      <c r="A501" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B501" s="82">
+        <v>46367</v>
+      </c>
+      <c r="C501" s="40">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="502" spans="1:3">
+      <c r="A502" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B502" s="82">
+        <v>46368</v>
+      </c>
+      <c r="C502" s="40">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="503" spans="1:3">
+      <c r="A503" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B503" s="82">
+        <v>46369</v>
+      </c>
+      <c r="C503" s="40">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="504" spans="1:3">
+      <c r="A504" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B504" s="82">
+        <v>46370</v>
+      </c>
+      <c r="C504" s="40">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="505" spans="1:3">
+      <c r="A505" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B505" s="82">
+        <v>46371</v>
+      </c>
+      <c r="C505" s="40">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="506" spans="1:3">
+      <c r="A506" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B506" s="82">
+        <v>46372</v>
+      </c>
+      <c r="C506" s="40">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="507" spans="1:3">
+      <c r="A507" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B507" s="82">
+        <v>46373</v>
+      </c>
+      <c r="C507" s="40">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="508" spans="1:3">
+      <c r="A508" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B508" s="82">
+        <v>46374</v>
+      </c>
+      <c r="C508" s="40">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="509" spans="1:3">
+      <c r="A509" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B509" s="82">
+        <v>46375</v>
+      </c>
+      <c r="C509" s="40">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="510" spans="1:3">
+      <c r="A510" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B510" s="82">
+        <v>46376</v>
+      </c>
+      <c r="C510" s="40">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="511" spans="1:3">
+      <c r="A511" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B511" s="82">
+        <v>46377</v>
+      </c>
+      <c r="C511" s="40">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="512" spans="1:3">
+      <c r="A512" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B512" s="82">
+        <v>46378</v>
+      </c>
+      <c r="C512" s="40">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="513" spans="1:3">
+      <c r="A513" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B513" s="82">
+        <v>46379</v>
+      </c>
+      <c r="C513" s="40">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="514" spans="1:3">
+      <c r="A514" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B514" s="82">
+        <v>46380</v>
+      </c>
+      <c r="C514" s="40">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="515" spans="1:3">
+      <c r="A515" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B515" s="82">
+        <v>46381</v>
+      </c>
+      <c r="C515" s="40">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="516" spans="1:3">
+      <c r="A516" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B516" s="82">
+        <v>46382</v>
+      </c>
+      <c r="C516" s="40">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="517" spans="1:3">
+      <c r="A517" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B517" s="82">
+        <v>46383</v>
+      </c>
+      <c r="C517" s="40">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="518" spans="1:3">
+      <c r="A518" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B518" s="82">
+        <v>46384</v>
+      </c>
+      <c r="C518" s="40">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="519" spans="1:3">
+      <c r="A519" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B519" s="82">
+        <v>46385</v>
+      </c>
+      <c r="C519" s="40">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="520" spans="1:3">
+      <c r="A520" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B520" s="82">
+        <v>46386</v>
+      </c>
+      <c r="C520" s="40">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="521" spans="1:3">
+      <c r="A521" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="B521" s="82">
+        <v>46387</v>
+      </c>
+      <c r="C521" s="40">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="522" spans="1:3">
+      <c r="A522" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B522" s="82">
+        <v>46296</v>
+      </c>
+      <c r="C522" s="40">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="523" spans="1:3">
+      <c r="A523" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B523" s="82">
+        <v>46297</v>
+      </c>
+      <c r="C523" s="40">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="524" spans="1:3">
+      <c r="A524" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B524" s="82">
+        <v>46298</v>
+      </c>
+      <c r="C524" s="40">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="525" spans="1:3">
+      <c r="A525" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B525" s="82">
+        <v>46299</v>
+      </c>
+      <c r="C525" s="40">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="526" spans="1:3">
+      <c r="A526" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B526" s="82">
+        <v>46300</v>
+      </c>
+      <c r="C526" s="40">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="527" spans="1:3">
+      <c r="A527" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B527" s="82">
+        <v>46301</v>
+      </c>
+      <c r="C527" s="40">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="528" spans="1:3">
+      <c r="A528" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B528" s="82">
+        <v>46302</v>
+      </c>
+      <c r="C528" s="40">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="529" spans="1:3">
+      <c r="A529" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B529" s="82">
+        <v>46303</v>
+      </c>
+      <c r="C529" s="40">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="530" spans="1:3">
+      <c r="A530" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B530" s="82">
+        <v>46304</v>
+      </c>
+      <c r="C530" s="40">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="531" spans="1:3">
+      <c r="A531" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B531" s="82">
+        <v>46305</v>
+      </c>
+      <c r="C531" s="40">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="532" spans="1:3">
+      <c r="A532" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B532" s="82">
+        <v>46306</v>
+      </c>
+      <c r="C532" s="40">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="533" spans="1:3">
+      <c r="A533" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B533" s="82">
+        <v>46307</v>
+      </c>
+      <c r="C533" s="40">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="534" spans="1:3">
+      <c r="A534" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B534" s="82">
+        <v>46308</v>
+      </c>
+      <c r="C534" s="40">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="535" spans="1:3">
+      <c r="A535" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B535" s="82">
+        <v>46309</v>
+      </c>
+      <c r="C535" s="40">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="536" spans="1:3">
+      <c r="A536" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B536" s="82">
+        <v>46310</v>
+      </c>
+      <c r="C536" s="40">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="537" spans="1:3">
+      <c r="A537" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B537" s="82">
+        <v>46311</v>
+      </c>
+      <c r="C537" s="40">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="538" spans="1:3">
+      <c r="A538" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B538" s="82">
+        <v>46312</v>
+      </c>
+      <c r="C538" s="40">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="539" spans="1:3">
+      <c r="A539" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B539" s="82">
+        <v>46313</v>
+      </c>
+      <c r="C539" s="40">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="540" spans="1:3">
+      <c r="A540" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B540" s="82">
+        <v>46314</v>
+      </c>
+      <c r="C540" s="40">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="541" spans="1:3">
+      <c r="A541" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B541" s="82">
+        <v>46315</v>
+      </c>
+      <c r="C541" s="40">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="542" spans="1:3">
+      <c r="A542" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B542" s="82">
+        <v>46316</v>
+      </c>
+      <c r="C542" s="40">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="543" spans="1:3">
+      <c r="A543" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B543" s="82">
+        <v>46317</v>
+      </c>
+      <c r="C543" s="40">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="544" spans="1:3">
+      <c r="A544" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B544" s="82">
+        <v>46318</v>
+      </c>
+      <c r="C544" s="40">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="545" spans="1:3">
+      <c r="A545" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B545" s="82">
+        <v>46319</v>
+      </c>
+      <c r="C545" s="40">
+        <f t="shared" si="9"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="546" spans="1:3">
+      <c r="A546" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B546" s="82">
+        <v>46320</v>
+      </c>
+      <c r="C546" s="40">
+        <f t="shared" ref="C546:C609" si="10">IF(D546="",100,MAX(0,(1440-D546)/1440*100))</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="547" spans="1:3">
+      <c r="A547" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B547" s="82">
+        <v>46321</v>
+      </c>
+      <c r="C547" s="40">
+        <f t="shared" si="10"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="548" spans="1:3">
+      <c r="A548" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B548" s="82">
+        <v>46322</v>
+      </c>
+      <c r="C548" s="40">
+        <f t="shared" si="10"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="549" spans="1:3">
+      <c r="A549" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B549" s="82">
+        <v>46323</v>
+      </c>
+      <c r="C549" s="40">
+        <f t="shared" si="10"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="550" spans="1:3">
+      <c r="A550" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B550" s="82">
+        <v>46324</v>
+      </c>
+      <c r="C550" s="40">
+        <f t="shared" si="10"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="551" spans="1:3">
+      <c r="A551" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B551" s="82">
+        <v>46325</v>
+      </c>
+      <c r="C551" s="40">
+        <f t="shared" si="10"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="552" spans="1:3">
+      <c r="A552" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B552" s="82">
+        <v>46326</v>
+      </c>
+      <c r="C552" s="40">
+        <f t="shared" si="10"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="553" spans="1:3">
+      <c r="A553" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B553" s="82">
+        <v>46327</v>
+      </c>
+      <c r="C553" s="40">
+        <f t="shared" si="10"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="554" spans="1:3">
+      <c r="A554" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B554" s="82">
+        <v>46328</v>
+      </c>
+      <c r="C554" s="40">
+        <f t="shared" si="10"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="555" spans="1:3">
+      <c r="A555" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B555" s="82">
+        <v>46329</v>
+      </c>
+      <c r="C555" s="40">
+        <f t="shared" si="10"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="556" spans="1:3">
+      <c r="A556" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B556" s="82">
+        <v>46330</v>
+      </c>
+      <c r="C556" s="40">
+        <f t="shared" si="10"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="557" spans="1:3">
+      <c r="A557" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B557" s="82">
+        <v>46331</v>
+      </c>
+      <c r="C557" s="40">
+        <f t="shared" si="10"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="558" spans="1:3">
+      <c r="A558" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B558" s="82">
+        <v>46332</v>
+      </c>
+      <c r="C558" s="40">
+        <f t="shared" si="10"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="559" spans="1:3">
+      <c r="A559" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B559" s="82">
+        <v>46333</v>
+      </c>
+      <c r="C559" s="40">
+        <f t="shared" si="10"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="560" spans="1:3">
+      <c r="A560" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B560" s="82">
+        <v>46334</v>
+      </c>
+      <c r="C560" s="40">
+        <f t="shared" si="10"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="561" spans="1:3">
+      <c r="A561" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B561" s="82">
+        <v>46335</v>
+      </c>
+      <c r="C561" s="40">
+        <f t="shared" si="10"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="562" spans="1:3">
+      <c r="A562" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B562" s="82">
+        <v>46336</v>
+      </c>
+      <c r="C562" s="40">
+        <f t="shared" si="10"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="563" spans="1:3">
+      <c r="A563" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B563" s="82">
+        <v>46337</v>
+      </c>
+      <c r="C563" s="40">
+        <f t="shared" si="10"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="564" spans="1:3">
+      <c r="A564" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B564" s="82">
+        <v>46338</v>
+      </c>
+      <c r="C564" s="40">
+        <f t="shared" si="10"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="565" spans="1:3">
+      <c r="A565" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B565" s="82">
+        <v>46339</v>
+      </c>
+      <c r="C565" s="40">
+        <f t="shared" si="10"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="566" spans="1:3">
+      <c r="A566" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B566" s="82">
+        <v>46340</v>
+      </c>
+      <c r="C566" s="40">
+        <f t="shared" si="10"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="567" spans="1:3">
+      <c r="A567" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B567" s="82">
+        <v>46341</v>
+      </c>
+      <c r="C567" s="40">
+        <f t="shared" si="10"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="568" spans="1:3">
+      <c r="A568" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B568" s="82">
+        <v>46342</v>
+      </c>
+      <c r="C568" s="40">
+        <f t="shared" si="10"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="569" spans="1:3">
+      <c r="A569" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B569" s="82">
+        <v>46343</v>
+      </c>
+      <c r="C569" s="40">
+        <f t="shared" si="10"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="570" spans="1:3">
+      <c r="A570" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B570" s="82">
+        <v>46344</v>
+      </c>
+      <c r="C570" s="40">
+        <f t="shared" si="10"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="571" spans="1:3">
+      <c r="A571" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B571" s="82">
+        <v>46345</v>
+      </c>
+      <c r="C571" s="40">
+        <f t="shared" si="10"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="572" spans="1:3">
+      <c r="A572" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B572" s="82">
+        <v>46346</v>
+      </c>
+      <c r="C572" s="40">
+        <f t="shared" si="10"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="573" spans="1:3">
+      <c r="A573" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B573" s="82">
+        <v>46347</v>
+      </c>
+      <c r="C573" s="40">
+        <f t="shared" si="10"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="574" spans="1:3">
+      <c r="A574" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B574" s="82">
+        <v>46348</v>
+      </c>
+      <c r="C574" s="40">
+        <f t="shared" si="10"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="575" spans="1:3">
+      <c r="A575" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B575" s="82">
+        <v>46349</v>
+      </c>
+      <c r="C575" s="40">
+        <f t="shared" si="10"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="576" spans="1:3">
+      <c r="A576" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B576" s="82">
+        <v>46350</v>
+      </c>
+      <c r="C576" s="40">
+        <f t="shared" si="10"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="577" spans="1:3">
+      <c r="A577" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B577" s="82">
+        <v>46351</v>
+      </c>
+      <c r="C577" s="40">
+        <f t="shared" si="10"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="578" spans="1:3">
+      <c r="A578" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B578" s="82">
+        <v>46352</v>
+      </c>
+      <c r="C578" s="40">
+        <f t="shared" si="10"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="579" spans="1:3">
+      <c r="A579" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B579" s="82">
+        <v>46353</v>
+      </c>
+      <c r="C579" s="40">
+        <f t="shared" si="10"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="580" spans="1:3">
+      <c r="A580" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B580" s="82">
+        <v>46354</v>
+      </c>
+      <c r="C580" s="40">
+        <f t="shared" si="10"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="581" spans="1:3">
+      <c r="A581" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B581" s="82">
+        <v>46355</v>
+      </c>
+      <c r="C581" s="40">
+        <f t="shared" si="10"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="582" spans="1:3">
+      <c r="A582" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B582" s="82">
+        <v>46356</v>
+      </c>
+      <c r="C582" s="40">
+        <f t="shared" si="10"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="583" spans="1:3">
+      <c r="A583" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B583" s="82">
+        <v>46357</v>
+      </c>
+      <c r="C583" s="40">
+        <f t="shared" si="10"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="584" spans="1:3">
+      <c r="A584" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B584" s="82">
+        <v>46358</v>
+      </c>
+      <c r="C584" s="40">
+        <f t="shared" si="10"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="585" spans="1:3">
+      <c r="A585" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B585" s="82">
+        <v>46359</v>
+      </c>
+      <c r="C585" s="40">
+        <f t="shared" si="10"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="586" spans="1:3">
+      <c r="A586" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B586" s="82">
+        <v>46360</v>
+      </c>
+      <c r="C586" s="40">
+        <f t="shared" si="10"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="587" spans="1:3">
+      <c r="A587" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B587" s="82">
+        <v>46361</v>
+      </c>
+      <c r="C587" s="40">
+        <f t="shared" si="10"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="588" spans="1:3">
+      <c r="A588" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B588" s="82">
+        <v>46362</v>
+      </c>
+      <c r="C588" s="40">
+        <f t="shared" si="10"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="589" spans="1:3">
+      <c r="A589" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B589" s="82">
+        <v>46363</v>
+      </c>
+      <c r="C589" s="40">
+        <f t="shared" si="10"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="590" spans="1:3">
+      <c r="A590" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B590" s="82">
+        <v>46364</v>
+      </c>
+      <c r="C590" s="40">
+        <f t="shared" si="10"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="591" spans="1:3">
+      <c r="A591" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B591" s="82">
+        <v>46365</v>
+      </c>
+      <c r="C591" s="40">
+        <f t="shared" si="10"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="592" spans="1:3">
+      <c r="A592" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B592" s="82">
+        <v>46366</v>
+      </c>
+      <c r="C592" s="40">
+        <f t="shared" si="10"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="593" spans="1:3">
+      <c r="A593" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B593" s="82">
+        <v>46367</v>
+      </c>
+      <c r="C593" s="40">
+        <f t="shared" si="10"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="594" spans="1:3">
+      <c r="A594" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B594" s="82">
+        <v>46368</v>
+      </c>
+      <c r="C594" s="40">
+        <f t="shared" si="10"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="595" spans="1:3">
+      <c r="A595" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B595" s="82">
+        <v>46369</v>
+      </c>
+      <c r="C595" s="40">
+        <f t="shared" si="10"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="596" spans="1:3">
+      <c r="A596" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B596" s="82">
+        <v>46370</v>
+      </c>
+      <c r="C596" s="40">
+        <f t="shared" si="10"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="597" spans="1:3">
+      <c r="A597" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B597" s="82">
+        <v>46371</v>
+      </c>
+      <c r="C597" s="40">
+        <f t="shared" si="10"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="598" spans="1:3">
+      <c r="A598" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B598" s="82">
+        <v>46372</v>
+      </c>
+      <c r="C598" s="40">
+        <f t="shared" si="10"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="599" spans="1:3">
+      <c r="A599" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B599" s="82">
+        <v>46373</v>
+      </c>
+      <c r="C599" s="40">
+        <f t="shared" si="10"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="600" spans="1:3">
+      <c r="A600" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B600" s="82">
+        <v>46374</v>
+      </c>
+      <c r="C600" s="40">
+        <f t="shared" si="10"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="601" spans="1:3">
+      <c r="A601" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B601" s="82">
+        <v>46375</v>
+      </c>
+      <c r="C601" s="40">
+        <f t="shared" si="10"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="602" spans="1:3">
+      <c r="A602" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B602" s="82">
+        <v>46376</v>
+      </c>
+      <c r="C602" s="40">
+        <f t="shared" si="10"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="603" spans="1:3">
+      <c r="A603" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B603" s="82">
+        <v>46377</v>
+      </c>
+      <c r="C603" s="40">
+        <f t="shared" si="10"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="604" spans="1:3">
+      <c r="A604" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B604" s="82">
+        <v>46378</v>
+      </c>
+      <c r="C604" s="40">
+        <f t="shared" si="10"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="605" spans="1:3">
+      <c r="A605" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B605" s="82">
+        <v>46379</v>
+      </c>
+      <c r="C605" s="40">
+        <f t="shared" si="10"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="606" spans="1:3">
+      <c r="A606" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B606" s="82">
+        <v>46380</v>
+      </c>
+      <c r="C606" s="40">
+        <f t="shared" si="10"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="607" spans="1:3">
+      <c r="A607" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B607" s="82">
+        <v>46381</v>
+      </c>
+      <c r="C607" s="40">
+        <f t="shared" si="10"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="608" spans="1:3">
+      <c r="A608" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B608" s="82">
+        <v>46382</v>
+      </c>
+      <c r="C608" s="40">
+        <f t="shared" si="10"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="609" spans="1:3">
+      <c r="A609" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B609" s="82">
+        <v>46383</v>
+      </c>
+      <c r="C609" s="40">
+        <f t="shared" si="10"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="610" spans="1:3">
+      <c r="A610" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B610" s="82">
+        <v>46384</v>
+      </c>
+      <c r="C610" s="40">
+        <f t="shared" ref="C610:C673" si="11">IF(D610="",100,MAX(0,(1440-D610)/1440*100))</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="611" spans="1:3">
+      <c r="A611" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B611" s="82">
+        <v>46385</v>
+      </c>
+      <c r="C611" s="40">
+        <f t="shared" si="11"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="612" spans="1:3">
+      <c r="A612" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B612" s="82">
+        <v>46386</v>
+      </c>
+      <c r="C612" s="40">
+        <f t="shared" si="11"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="613" spans="1:3">
+      <c r="A613" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B613" s="82">
+        <v>46387</v>
+      </c>
+      <c r="C613" s="40">
+        <f t="shared" si="11"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="614" spans="1:3">
+      <c r="A614" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B614" s="82">
+        <v>46296</v>
+      </c>
+      <c r="C614" s="40">
+        <f t="shared" si="11"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="615" spans="1:3">
+      <c r="A615" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B615" s="82">
+        <v>46297</v>
+      </c>
+      <c r="C615" s="40">
+        <f t="shared" si="11"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="616" spans="1:3">
+      <c r="A616" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B616" s="82">
+        <v>46298</v>
+      </c>
+      <c r="C616" s="40">
+        <f t="shared" si="11"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="617" spans="1:3">
+      <c r="A617" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B617" s="82">
+        <v>46299</v>
+      </c>
+      <c r="C617" s="40">
+        <f t="shared" si="11"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="618" spans="1:3">
+      <c r="A618" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B618" s="82">
+        <v>46300</v>
+      </c>
+      <c r="C618" s="40">
+        <f t="shared" si="11"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="619" spans="1:3">
+      <c r="A619" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B619" s="82">
+        <v>46301</v>
+      </c>
+      <c r="C619" s="40">
+        <f t="shared" si="11"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="620" spans="1:3">
+      <c r="A620" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B620" s="82">
+        <v>46302</v>
+      </c>
+      <c r="C620" s="40">
+        <f t="shared" si="11"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="621" spans="1:3">
+      <c r="A621" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B621" s="82">
+        <v>46303</v>
+      </c>
+      <c r="C621" s="40">
+        <f t="shared" si="11"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="622" spans="1:3">
+      <c r="A622" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B622" s="82">
+        <v>46304</v>
+      </c>
+      <c r="C622" s="40">
+        <f t="shared" si="11"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="623" spans="1:3">
+      <c r="A623" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B623" s="82">
+        <v>46305</v>
+      </c>
+      <c r="C623" s="40">
+        <f t="shared" si="11"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="624" spans="1:3">
+      <c r="A624" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B624" s="82">
+        <v>46306</v>
+      </c>
+      <c r="C624" s="40">
+        <f t="shared" si="11"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="625" spans="1:3">
+      <c r="A625" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B625" s="82">
+        <v>46307</v>
+      </c>
+      <c r="C625" s="40">
+        <f t="shared" si="11"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="626" spans="1:3">
+      <c r="A626" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B626" s="82">
+        <v>46308</v>
+      </c>
+      <c r="C626" s="40">
+        <f t="shared" si="11"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="627" spans="1:3">
+      <c r="A627" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B627" s="82">
+        <v>46309</v>
+      </c>
+      <c r="C627" s="40">
+        <f t="shared" si="11"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="628" spans="1:3">
+      <c r="A628" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B628" s="82">
+        <v>46310</v>
+      </c>
+      <c r="C628" s="40">
+        <f t="shared" si="11"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="629" spans="1:3">
+      <c r="A629" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B629" s="82">
+        <v>46311</v>
+      </c>
+      <c r="C629" s="40">
+        <f t="shared" si="11"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="630" spans="1:3">
+      <c r="A630" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B630" s="82">
+        <v>46312</v>
+      </c>
+      <c r="C630" s="40">
+        <f t="shared" si="11"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="631" spans="1:3">
+      <c r="A631" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B631" s="82">
+        <v>46313</v>
+      </c>
+      <c r="C631" s="40">
+        <f t="shared" si="11"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="632" spans="1:3">
+      <c r="A632" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B632" s="82">
+        <v>46314</v>
+      </c>
+      <c r="C632" s="40">
+        <f t="shared" si="11"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="633" spans="1:3">
+      <c r="A633" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B633" s="82">
+        <v>46315</v>
+      </c>
+      <c r="C633" s="40">
+        <f t="shared" si="11"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="634" spans="1:3">
+      <c r="A634" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B634" s="82">
+        <v>46316</v>
+      </c>
+      <c r="C634" s="40">
+        <f t="shared" si="11"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="635" spans="1:3">
+      <c r="A635" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B635" s="82">
+        <v>46317</v>
+      </c>
+      <c r="C635" s="40">
+        <f t="shared" si="11"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="636" spans="1:3">
+      <c r="A636" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B636" s="82">
+        <v>46318</v>
+      </c>
+      <c r="C636" s="40">
+        <f t="shared" si="11"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="637" spans="1:3">
+      <c r="A637" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B637" s="82">
+        <v>46319</v>
+      </c>
+      <c r="C637" s="40">
+        <f t="shared" si="11"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="638" spans="1:3">
+      <c r="A638" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B638" s="82">
+        <v>46320</v>
+      </c>
+      <c r="C638" s="40">
+        <f t="shared" si="11"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="639" spans="1:3">
+      <c r="A639" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B639" s="82">
+        <v>46321</v>
+      </c>
+      <c r="C639" s="40">
+        <f t="shared" si="11"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="640" spans="1:3">
+      <c r="A640" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B640" s="82">
+        <v>46322</v>
+      </c>
+      <c r="C640" s="40">
+        <f t="shared" si="11"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="641" spans="1:3">
+      <c r="A641" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B641" s="82">
+        <v>46323</v>
+      </c>
+      <c r="C641" s="40">
+        <f t="shared" si="11"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="642" spans="1:3">
+      <c r="A642" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B642" s="82">
+        <v>46324</v>
+      </c>
+      <c r="C642" s="40">
+        <f t="shared" si="11"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="643" spans="1:3">
+      <c r="A643" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B643" s="82">
+        <v>46325</v>
+      </c>
+      <c r="C643" s="40">
+        <f t="shared" si="11"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="644" spans="1:3">
+      <c r="A644" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B644" s="82">
+        <v>46326</v>
+      </c>
+      <c r="C644" s="40">
+        <f t="shared" si="11"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="645" spans="1:3">
+      <c r="A645" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B645" s="82">
+        <v>46327</v>
+      </c>
+      <c r="C645" s="40">
+        <f t="shared" si="11"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="646" spans="1:3">
+      <c r="A646" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B646" s="82">
+        <v>46328</v>
+      </c>
+      <c r="C646" s="40">
+        <f t="shared" si="11"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="647" spans="1:3">
+      <c r="A647" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B647" s="82">
+        <v>46329</v>
+      </c>
+      <c r="C647" s="40">
+        <f t="shared" si="11"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="648" spans="1:3">
+      <c r="A648" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B648" s="82">
+        <v>46330</v>
+      </c>
+      <c r="C648" s="40">
+        <f t="shared" si="11"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="649" spans="1:3">
+      <c r="A649" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B649" s="82">
+        <v>46331</v>
+      </c>
+      <c r="C649" s="40">
+        <f t="shared" si="11"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="650" spans="1:3">
+      <c r="A650" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B650" s="82">
+        <v>46332</v>
+      </c>
+      <c r="C650" s="40">
+        <f t="shared" si="11"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="651" spans="1:3">
+      <c r="A651" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B651" s="82">
+        <v>46333</v>
+      </c>
+      <c r="C651" s="40">
+        <f t="shared" si="11"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="652" spans="1:3">
+      <c r="A652" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B652" s="82">
+        <v>46334</v>
+      </c>
+      <c r="C652" s="40">
+        <f t="shared" si="11"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="653" spans="1:3">
+      <c r="A653" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B653" s="82">
+        <v>46335</v>
+      </c>
+      <c r="C653" s="40">
+        <f t="shared" si="11"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="654" spans="1:3">
+      <c r="A654" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B654" s="82">
+        <v>46336</v>
+      </c>
+      <c r="C654" s="40">
+        <f t="shared" si="11"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="655" spans="1:3">
+      <c r="A655" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B655" s="82">
+        <v>46337</v>
+      </c>
+      <c r="C655" s="40">
+        <f t="shared" si="11"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="656" spans="1:3">
+      <c r="A656" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B656" s="82">
+        <v>46338</v>
+      </c>
+      <c r="C656" s="40">
+        <f t="shared" si="11"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="657" spans="1:3">
+      <c r="A657" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B657" s="82">
+        <v>46339</v>
+      </c>
+      <c r="C657" s="40">
+        <f t="shared" si="11"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="658" spans="1:3">
+      <c r="A658" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B658" s="82">
+        <v>46340</v>
+      </c>
+      <c r="C658" s="40">
+        <f t="shared" si="11"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="659" spans="1:3">
+      <c r="A659" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B659" s="82">
+        <v>46341</v>
+      </c>
+      <c r="C659" s="40">
+        <f t="shared" si="11"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="660" spans="1:3">
+      <c r="A660" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B660" s="82">
+        <v>46342</v>
+      </c>
+      <c r="C660" s="40">
+        <f t="shared" si="11"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="661" spans="1:3">
+      <c r="A661" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B661" s="82">
+        <v>46343</v>
+      </c>
+      <c r="C661" s="40">
+        <f t="shared" si="11"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="662" spans="1:3">
+      <c r="A662" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B662" s="82">
+        <v>46344</v>
+      </c>
+      <c r="C662" s="40">
+        <f t="shared" si="11"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="663" spans="1:3">
+      <c r="A663" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B663" s="82">
+        <v>46345</v>
+      </c>
+      <c r="C663" s="40">
+        <f t="shared" si="11"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="664" spans="1:3">
+      <c r="A664" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B664" s="82">
+        <v>46346</v>
+      </c>
+      <c r="C664" s="40">
+        <f t="shared" si="11"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="665" spans="1:3">
+      <c r="A665" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B665" s="82">
+        <v>46347</v>
+      </c>
+      <c r="C665" s="40">
+        <f t="shared" si="11"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="666" spans="1:3">
+      <c r="A666" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B666" s="82">
+        <v>46348</v>
+      </c>
+      <c r="C666" s="40">
+        <f t="shared" si="11"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="667" spans="1:3">
+      <c r="A667" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B667" s="82">
+        <v>46349</v>
+      </c>
+      <c r="C667" s="40">
+        <f t="shared" si="11"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="668" spans="1:3">
+      <c r="A668" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B668" s="82">
+        <v>46350</v>
+      </c>
+      <c r="C668" s="40">
+        <f t="shared" si="11"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="669" spans="1:3">
+      <c r="A669" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B669" s="82">
+        <v>46351</v>
+      </c>
+      <c r="C669" s="40">
+        <f t="shared" si="11"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="670" spans="1:3">
+      <c r="A670" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B670" s="82">
+        <v>46352</v>
+      </c>
+      <c r="C670" s="40">
+        <f t="shared" si="11"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="671" spans="1:3">
+      <c r="A671" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B671" s="82">
+        <v>46353</v>
+      </c>
+      <c r="C671" s="40">
+        <f t="shared" si="11"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="672" spans="1:3">
+      <c r="A672" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B672" s="82">
+        <v>46354</v>
+      </c>
+      <c r="C672" s="40">
+        <f t="shared" si="11"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="673" spans="1:3">
+      <c r="A673" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B673" s="82">
+        <v>46355</v>
+      </c>
+      <c r="C673" s="40">
+        <f t="shared" si="11"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="674" spans="1:3">
+      <c r="A674" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B674" s="82">
+        <v>46356</v>
+      </c>
+      <c r="C674" s="40">
+        <f t="shared" ref="C674:C705" si="12">IF(D674="",100,MAX(0,(1440-D674)/1440*100))</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="675" spans="1:3">
+      <c r="A675" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B675" s="82">
+        <v>46357</v>
+      </c>
+      <c r="C675" s="40">
+        <f t="shared" si="12"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="676" spans="1:3">
+      <c r="A676" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B676" s="82">
+        <v>46358</v>
+      </c>
+      <c r="C676" s="40">
+        <f t="shared" si="12"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="677" spans="1:3">
+      <c r="A677" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B677" s="82">
+        <v>46359</v>
+      </c>
+      <c r="C677" s="40">
+        <f t="shared" si="12"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="678" spans="1:3">
+      <c r="A678" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B678" s="82">
+        <v>46360</v>
+      </c>
+      <c r="C678" s="40">
+        <f t="shared" si="12"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="679" spans="1:3">
+      <c r="A679" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B679" s="82">
+        <v>46361</v>
+      </c>
+      <c r="C679" s="40">
+        <f t="shared" si="12"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="680" spans="1:3">
+      <c r="A680" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B680" s="82">
+        <v>46362</v>
+      </c>
+      <c r="C680" s="40">
+        <f t="shared" si="12"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="681" spans="1:3">
+      <c r="A681" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B681" s="82">
+        <v>46363</v>
+      </c>
+      <c r="C681" s="40">
+        <f t="shared" si="12"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="682" spans="1:3">
+      <c r="A682" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B682" s="82">
+        <v>46364</v>
+      </c>
+      <c r="C682" s="40">
+        <f t="shared" si="12"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="683" spans="1:3">
+      <c r="A683" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B683" s="82">
+        <v>46365</v>
+      </c>
+      <c r="C683" s="40">
+        <f t="shared" si="12"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="684" spans="1:3">
+      <c r="A684" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B684" s="82">
+        <v>46366</v>
+      </c>
+      <c r="C684" s="40">
+        <f t="shared" si="12"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="685" spans="1:3">
+      <c r="A685" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B685" s="82">
+        <v>46367</v>
+      </c>
+      <c r="C685" s="40">
+        <f t="shared" si="12"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="686" spans="1:3">
+      <c r="A686" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B686" s="82">
+        <v>46368</v>
+      </c>
+      <c r="C686" s="40">
+        <f t="shared" si="12"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="687" spans="1:3">
+      <c r="A687" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B687" s="82">
+        <v>46369</v>
+      </c>
+      <c r="C687" s="40">
+        <f t="shared" si="12"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="688" spans="1:3">
+      <c r="A688" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B688" s="82">
+        <v>46370</v>
+      </c>
+      <c r="C688" s="40">
+        <f t="shared" si="12"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="689" spans="1:3">
+      <c r="A689" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B689" s="82">
+        <v>46371</v>
+      </c>
+      <c r="C689" s="40">
+        <f t="shared" si="12"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="690" spans="1:3">
+      <c r="A690" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B690" s="82">
+        <v>46372</v>
+      </c>
+      <c r="C690" s="40">
+        <f t="shared" si="12"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="691" spans="1:3">
+      <c r="A691" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B691" s="82">
+        <v>46373</v>
+      </c>
+      <c r="C691" s="40">
+        <f t="shared" si="12"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="692" spans="1:3">
+      <c r="A692" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B692" s="82">
+        <v>46374</v>
+      </c>
+      <c r="C692" s="40">
+        <f t="shared" si="12"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="693" spans="1:3">
+      <c r="A693" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B693" s="82">
+        <v>46375</v>
+      </c>
+      <c r="C693" s="40">
+        <f t="shared" si="12"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="694" spans="1:3">
+      <c r="A694" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B694" s="82">
+        <v>46376</v>
+      </c>
+      <c r="C694" s="40">
+        <f t="shared" si="12"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="695" spans="1:3">
+      <c r="A695" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B695" s="82">
+        <v>46377</v>
+      </c>
+      <c r="C695" s="40">
+        <f t="shared" si="12"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="696" spans="1:3">
+      <c r="A696" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B696" s="82">
+        <v>46378</v>
+      </c>
+      <c r="C696" s="40">
+        <f t="shared" si="12"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="697" spans="1:3">
+      <c r="A697" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B697" s="82">
+        <v>46379</v>
+      </c>
+      <c r="C697" s="40">
+        <f t="shared" si="12"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="698" spans="1:3">
+      <c r="A698" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B698" s="82">
+        <v>46380</v>
+      </c>
+      <c r="C698" s="40">
+        <f t="shared" si="12"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="699" spans="1:3">
+      <c r="A699" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B699" s="82">
+        <v>46381</v>
+      </c>
+      <c r="C699" s="40">
+        <f t="shared" si="12"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="700" spans="1:3">
+      <c r="A700" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B700" s="82">
+        <v>46382</v>
+      </c>
+      <c r="C700" s="40">
+        <f t="shared" si="12"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="701" spans="1:3">
+      <c r="A701" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B701" s="82">
+        <v>46383</v>
+      </c>
+      <c r="C701" s="40">
+        <f t="shared" si="12"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="702" spans="1:3">
+      <c r="A702" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B702" s="82">
+        <v>46384</v>
+      </c>
+      <c r="C702" s="40">
+        <f t="shared" si="12"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="703" spans="1:3">
+      <c r="A703" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B703" s="82">
+        <v>46385</v>
+      </c>
+      <c r="C703" s="40">
+        <f t="shared" si="12"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="704" spans="1:3">
+      <c r="A704" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B704" s="82">
+        <v>46386</v>
+      </c>
+      <c r="C704" s="40">
+        <f t="shared" si="12"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="705" spans="1:3">
+      <c r="A705" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B705" s="82">
+        <v>46387</v>
+      </c>
+      <c r="C705" s="40">
+        <f t="shared" si="12"/>
         <v>100</v>
       </c>
     </row>
@@ -17545,7 +23068,7 @@
     </sortState>
   </autoFilter>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A245" xr:uid="{D87D8A40-72F0-47F9-B708-8FE8197B5EB9}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A705" xr:uid="{D87D8A40-72F0-47F9-B708-8FE8197B5EB9}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/Data/#U0e23#U0e32#U0e22#U0e07#U0e32#U0e19#U0e1b#U0e23#U0e30#U0e08#U0e33#U0e27#U0e31#U0e19#U0e0a#U0e38#U0e21#U0e2a#U0e32#U0e22 v2.5.xlsx
+++ b/Data/#U0e23#U0e32#U0e22#U0e07#U0e32#U0e19#U0e1b#U0e23#U0e30#U0e08#U0e33#U0e27#U0e31#U0e19#U0e0a#U0e38#U0e21#U0e2a#U0e32#U0e22 v2.5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Forth\0.USO\Anitigravity\Gang3Cha\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5036545-E0CC-4734-916D-578D7D61B5B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBD3E309-8D98-4B94-A48D-273D8904C005}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="202" r:id="rId1"/>
